--- a/addresses/good_addresses.xlsx
+++ b/addresses/good_addresses.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\routecraft\addresses\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDA82F44-96F8-4D6D-95C4-07285B0D0F89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="82">
   <si>
     <t>City</t>
   </si>
@@ -112,111 +111,171 @@
     <t>41</t>
   </si>
   <si>
-    <t>משך חכמה</t>
-  </si>
-  <si>
-    <t>64</t>
-  </si>
-  <si>
-    <t>חפץ חיים</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>45</t>
-  </si>
-  <si>
-    <t>מסילת יוסף</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>רחוב עקיבא</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>שאגת אריה</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>רב ושמואל</t>
-  </si>
-  <si>
-    <t>עיון התלמוד</t>
-  </si>
-  <si>
-    <t>רשבא</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>חתם סופר</t>
-  </si>
-  <si>
-    <t>הבעל שם טוב</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>קהילות יעקב</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>שדרות יחזקאל</t>
-  </si>
-  <si>
-    <t>31</t>
-  </si>
-  <si>
-    <t>מרומי שדה</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>אורח חיים</t>
-  </si>
-  <si>
-    <t>37</t>
-  </si>
-  <si>
-    <t>פונוביז</t>
-  </si>
-  <si>
-    <t>נתיבות המשפט</t>
-  </si>
-  <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>חזון דוד</t>
-  </si>
-  <si>
-    <t>2</t>
+    <t>לוד</t>
+  </si>
+  <si>
+    <t xml:space="preserve">יחד שבטי ישראל </t>
+  </si>
+  <si>
+    <t xml:space="preserve">משה רבינו </t>
+  </si>
+  <si>
+    <t xml:space="preserve">השייטת </t>
+  </si>
+  <si>
+    <t xml:space="preserve">צמח צדק </t>
+  </si>
+  <si>
+    <t xml:space="preserve">שבט יהודה </t>
+  </si>
+  <si>
+    <t xml:space="preserve">שבט אשר </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> שבט יהודה</t>
+  </si>
+  <si>
+    <t xml:space="preserve">אחיסמך רבקה אימנו </t>
+  </si>
+  <si>
+    <t xml:space="preserve">שבט זבולון </t>
+  </si>
+  <si>
+    <t>עפולה</t>
+  </si>
+  <si>
+    <t>קונטיקט 5</t>
+  </si>
+  <si>
+    <t>הזהבן 4</t>
+  </si>
+  <si>
+    <t>חיננית 13</t>
+  </si>
+  <si>
+    <t>חטפית 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">פנקס צבי 8 </t>
+  </si>
+  <si>
+    <t>צוקית 9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">הרצל 19 </t>
+  </si>
+  <si>
+    <t>עלית הנוער 8</t>
+  </si>
+  <si>
+    <t>רחוב הרצל 24</t>
+  </si>
+  <si>
+    <t>הבריגדה היהודית 11</t>
+  </si>
+  <si>
+    <t>אבן גבירול 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">זבוטינסקי 10 </t>
+  </si>
+  <si>
+    <t>הרוגי מלכות 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">עליית הנוער 9 </t>
+  </si>
+  <si>
+    <t>ראסל 10</t>
+  </si>
+  <si>
+    <t>ירקון 11</t>
+  </si>
+  <si>
+    <t>אבן גבירול 45</t>
+  </si>
+  <si>
+    <t>אבן גבירול 30</t>
+  </si>
+  <si>
+    <t>רכסים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">רחוב סביון </t>
+  </si>
+  <si>
+    <t xml:space="preserve">הכלניות </t>
+  </si>
+  <si>
+    <t xml:space="preserve">כלניות </t>
+  </si>
+  <si>
+    <t xml:space="preserve">הורדים  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ורדים </t>
+  </si>
+  <si>
+    <t xml:space="preserve">הנרקיסים  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">הנרקיסים </t>
+  </si>
+  <si>
+    <t xml:space="preserve">הכלניות  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">רחוב הזית </t>
+  </si>
+  <si>
+    <t xml:space="preserve">הדקל </t>
+  </si>
+  <si>
+    <t xml:space="preserve">הדס </t>
+  </si>
+  <si>
+    <t xml:space="preserve">הדס  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">אשל </t>
+  </si>
+  <si>
+    <t xml:space="preserve">דקל </t>
+  </si>
+  <si>
+    <t xml:space="preserve">השקד  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">השקד </t>
+  </si>
+  <si>
+    <t xml:space="preserve">מעלה החזון איש </t>
+  </si>
+  <si>
+    <t xml:space="preserve">חזון איש </t>
+  </si>
+  <si>
+    <t xml:space="preserve">רימונים </t>
+  </si>
+  <si>
+    <t xml:space="preserve">הרימונים </t>
+  </si>
+  <si>
+    <t xml:space="preserve">הרב קוק  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">הרב קוק </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -224,7 +283,7 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -255,13 +314,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -564,13 +630,13 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E261"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.8984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.59765625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.3984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -751,7 +817,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>3</v>
       </c>
@@ -762,7 +828,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>3</v>
       </c>
@@ -773,539 +839,846 @@
         <v>28</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="B19" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="C19" s="4" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+      <c r="D19" s="3"/>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="B20" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="C20" s="4" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+      <c r="D20" s="3"/>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C21" s="4">
+        <v>46</v>
+      </c>
+      <c r="D21" s="3"/>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C22" s="4">
+        <v>6</v>
+      </c>
+      <c r="D22" s="3"/>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C23" s="4">
         <v>3</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="D23" s="3"/>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="B24" s="5" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+      <c r="C24" s="4">
+        <v>8</v>
+      </c>
+      <c r="D24" s="3"/>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C25" s="4">
+        <v>5</v>
+      </c>
+      <c r="D25" s="3"/>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C26" s="4">
+        <v>7</v>
+      </c>
+      <c r="D26" s="3"/>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C27" s="4">
+        <v>7</v>
+      </c>
+      <c r="D27" s="3"/>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C28" s="4">
+        <v>7</v>
+      </c>
+      <c r="D28" s="3"/>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C29" s="4">
+        <v>12</v>
+      </c>
+      <c r="D29" s="3"/>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C30" s="4">
+        <v>7</v>
+      </c>
+      <c r="D30" s="3"/>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C31" s="4">
         <v>3</v>
       </c>
-      <c r="B22" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>3</v>
-      </c>
-      <c r="B23" s="1" t="s">
+      <c r="D31" s="3"/>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C32" s="4">
+        <v>5</v>
+      </c>
+      <c r="D32" s="3"/>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="C33" s="4">
+        <v>43</v>
+      </c>
+      <c r="D33" s="3"/>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C34" s="4">
         <v>8</v>
       </c>
-      <c r="C23" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>3</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>3</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>3</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>3</v>
-      </c>
-      <c r="B27" s="1" t="s">
+      <c r="D34" s="3"/>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C35" s="4">
+        <v>15</v>
+      </c>
+      <c r="D35" s="3"/>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C36" s="4">
+        <v>11</v>
+      </c>
+      <c r="D36" s="3"/>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C37" s="4">
+        <v>5</v>
+      </c>
+      <c r="D37" s="3"/>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C38" s="4">
+        <v>4</v>
+      </c>
+      <c r="D38" s="3"/>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>40</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C39" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>40</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C40" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>40</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C41" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>40</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C42" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>40</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C43" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>40</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C44" s="1">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>40</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C45" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>40</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C46" s="1">
         <v>24</v>
       </c>
-      <c r="C27" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>3</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>3</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C29" s="1" t="s">
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>3</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>3</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>3</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>3</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>3</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>3</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>3</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C36" s="1" t="s">
+      <c r="B47" s="1" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>3</v>
-      </c>
-      <c r="B37" s="1" t="s">
+      <c r="C47" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>40</v>
+      </c>
+      <c r="B48" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C37" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>3</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>3</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>3</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>3</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>3</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>3</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>3</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>3</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>3</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>3</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>3</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>47</v>
+      <c r="C48" s="1">
+        <v>4</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>61</v>
+        <v>52</v>
+      </c>
+      <c r="C49" s="1">
+        <v>10</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C50" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C50" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>40</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C51" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>40</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C52" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>40</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C53" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>40</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C54" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>40</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C55" s="1">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>40</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C56" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>59</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C57" s="1">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>59</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C58" s="1">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>59</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C59" s="1">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>59</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C60" s="1">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>59</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C61" s="1">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>59</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C62" s="1">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>59</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C63" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>59</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C64" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>59</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C65" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>59</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C66" s="1">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>59</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C67" s="1">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>59</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C68" s="1">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>59</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C69" s="1">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>59</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C70" s="1">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>59</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C71" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>59</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C72" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>59</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C73" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>59</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C74" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>59</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C75" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>59</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C76" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>59</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C77" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>59</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C78" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>59</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C79" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>59</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C80" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>59</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C81" s="1">
         <v>50</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B51" s="1"/>
-      <c r="C51" s="1"/>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B52" s="1"/>
-      <c r="C52" s="1"/>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B53" s="1"/>
-      <c r="C53" s="1"/>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B54" s="1"/>
-      <c r="C54" s="1"/>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B55" s="1"/>
-      <c r="C55" s="1"/>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B56" s="1"/>
-      <c r="C56" s="1"/>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B57" s="1"/>
-      <c r="C57" s="1"/>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B58" s="1"/>
-      <c r="C58" s="1"/>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B59" s="1"/>
-      <c r="C59" s="1"/>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B60" s="1"/>
-      <c r="C60" s="1"/>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B61" s="1"/>
-      <c r="C61" s="1"/>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B62" s="1"/>
-      <c r="C62" s="1"/>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B63" s="1"/>
-      <c r="C63" s="1"/>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B64" s="1"/>
-      <c r="C64" s="1"/>
-    </row>
-    <row r="65" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B65" s="1"/>
-      <c r="C65" s="1"/>
-    </row>
-    <row r="66" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B66" s="1"/>
-      <c r="C66" s="1"/>
-    </row>
-    <row r="67" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B67" s="1"/>
-      <c r="C67" s="1"/>
-    </row>
-    <row r="68" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B68" s="1"/>
-      <c r="C68" s="1"/>
-    </row>
-    <row r="69" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B69" s="1"/>
-      <c r="C69" s="1"/>
-    </row>
-    <row r="70" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B70" s="1"/>
-      <c r="C70" s="1"/>
-    </row>
-    <row r="71" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B71" s="1"/>
-      <c r="C71" s="1"/>
-    </row>
-    <row r="72" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B72" s="1"/>
-      <c r="C72" s="1"/>
-    </row>
-    <row r="73" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B73" s="1"/>
-      <c r="C73" s="1"/>
-    </row>
-    <row r="74" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B74" s="1"/>
-      <c r="C74" s="1"/>
-    </row>
-    <row r="75" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B75" s="1"/>
-      <c r="C75" s="1"/>
-    </row>
-    <row r="76" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B76" s="1"/>
-      <c r="C76" s="1"/>
-    </row>
-    <row r="77" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B77" s="1"/>
-      <c r="C77" s="1"/>
-    </row>
-    <row r="78" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B78" s="1"/>
-      <c r="C78" s="1"/>
-    </row>
-    <row r="79" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B79" s="1"/>
-      <c r="C79" s="1"/>
-    </row>
-    <row r="80" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B80" s="1"/>
-      <c r="C80" s="1"/>
-    </row>
-    <row r="81" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B81" s="1"/>
-      <c r="C81" s="1"/>
-    </row>
-    <row r="82" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B82" s="1"/>
-      <c r="C82" s="1"/>
-    </row>
-    <row r="83" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B83" s="1"/>
-      <c r="C83" s="1"/>
-    </row>
-    <row r="84" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B84" s="1"/>
-      <c r="C84" s="1"/>
-    </row>
-    <row r="85" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B85" s="1"/>
-      <c r="C85" s="1"/>
-    </row>
-    <row r="86" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B86" s="1"/>
-      <c r="C86" s="1"/>
-    </row>
-    <row r="87" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B87" s="1"/>
-      <c r="C87" s="1"/>
-    </row>
-    <row r="88" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B88" s="1"/>
-      <c r="C88" s="1"/>
-    </row>
-    <row r="89" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B89" s="1"/>
-      <c r="C89" s="1"/>
-    </row>
-    <row r="90" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B90" s="1"/>
-      <c r="C90" s="1"/>
-    </row>
-    <row r="91" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B91" s="1"/>
-      <c r="C91" s="1"/>
-    </row>
-    <row r="92" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>59</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C82" s="1">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>59</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C83" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>59</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C84" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>59</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C85" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>59</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C86" s="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>59</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C87" s="1">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>59</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C88" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>59</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C89" s="1">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>59</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C90" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>59</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C91" s="1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B92" s="1"/>
       <c r="C92" s="1"/>
     </row>
-    <row r="93" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B93" s="1"/>
       <c r="C93" s="1"/>
     </row>
-    <row r="94" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B94" s="1"/>
       <c r="C94" s="1"/>
     </row>
-    <row r="95" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B95" s="1"/>
       <c r="C95" s="1"/>
     </row>
-    <row r="96" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B96" s="1"/>
       <c r="C96" s="1"/>
     </row>

--- a/addresses/good_addresses.xlsx
+++ b/addresses/good_addresses.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="98">
   <si>
     <t>City</t>
   </si>
@@ -141,63 +141,6 @@
     <t xml:space="preserve">שבט זבולון </t>
   </si>
   <si>
-    <t>עפולה</t>
-  </si>
-  <si>
-    <t>קונטיקט 5</t>
-  </si>
-  <si>
-    <t>הזהבן 4</t>
-  </si>
-  <si>
-    <t>חיננית 13</t>
-  </si>
-  <si>
-    <t>חטפית 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">פנקס צבי 8 </t>
-  </si>
-  <si>
-    <t>צוקית 9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">הרצל 19 </t>
-  </si>
-  <si>
-    <t>עלית הנוער 8</t>
-  </si>
-  <si>
-    <t>רחוב הרצל 24</t>
-  </si>
-  <si>
-    <t>הבריגדה היהודית 11</t>
-  </si>
-  <si>
-    <t>אבן גבירול 4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">זבוטינסקי 10 </t>
-  </si>
-  <si>
-    <t>הרוגי מלכות 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">עליית הנוער 9 </t>
-  </si>
-  <si>
-    <t>ראסל 10</t>
-  </si>
-  <si>
-    <t>ירקון 11</t>
-  </si>
-  <si>
-    <t>אבן גבירול 45</t>
-  </si>
-  <si>
-    <t>אבן גבירול 30</t>
-  </si>
-  <si>
     <t>רכסים</t>
   </si>
   <si>
@@ -265,6 +208,111 @@
   </si>
   <si>
     <t xml:space="preserve">הרב קוק </t>
+  </si>
+  <si>
+    <t xml:space="preserve">משה רבינו  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">צמח צדק  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">שבט יהודה  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">שבט אשר  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> שבט זבולון</t>
+  </si>
+  <si>
+    <t xml:space="preserve">יעקב אבינו </t>
+  </si>
+  <si>
+    <t xml:space="preserve">בעל התניא </t>
+  </si>
+  <si>
+    <t xml:space="preserve">שבט אפרים </t>
+  </si>
+  <si>
+    <t xml:space="preserve">שבטי ישראל </t>
+  </si>
+  <si>
+    <t xml:space="preserve">הרב עובדיה יוסף </t>
+  </si>
+  <si>
+    <t xml:space="preserve">משה רבנו </t>
+  </si>
+  <si>
+    <t xml:space="preserve">יצחק אבינו </t>
+  </si>
+  <si>
+    <t>חתם סופר</t>
+  </si>
+  <si>
+    <t>37</t>
+  </si>
+  <si>
+    <t>שדי חמד</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>אור החיים</t>
+  </si>
+  <si>
+    <t>חזון דוד</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>נתיבות המשפט</t>
+  </si>
+  <si>
+    <t>93</t>
+  </si>
+  <si>
+    <t>מסילת יוסף</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>85</t>
+  </si>
+  <si>
+    <t>משך חכמה</t>
+  </si>
+  <si>
+    <t>80</t>
+  </si>
+  <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t>שאגת אריה</t>
+  </si>
+  <si>
+    <t>רמבם</t>
+  </si>
+  <si>
+    <t>71</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>אבני נזר</t>
+  </si>
+  <si>
+    <t>מסילת ישרים</t>
+  </si>
+  <si>
+    <t>40</t>
   </si>
 </sst>
 </file>
@@ -314,7 +362,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -328,6 +376,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -631,12 +682,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E261"/>
+  <dimension ref="A1:H261"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.8984375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17.59765625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.3984375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="17.69921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -864,244 +916,254 @@
       <c r="D20" s="3"/>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C21" s="4">
-        <v>46</v>
+      <c r="A21" t="s">
+        <v>3</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>15</v>
       </c>
       <c r="D21" s="3"/>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C22" s="4">
-        <v>6</v>
+      <c r="A22" t="s">
+        <v>3</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>76</v>
       </c>
       <c r="D22" s="3"/>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="C23" s="4">
-        <v>3</v>
+      <c r="A23" t="s">
+        <v>3</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>78</v>
       </c>
       <c r="D23" s="3"/>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C24" s="4">
-        <v>8</v>
+      <c r="A24" t="s">
+        <v>3</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="D24" s="3"/>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="C25" s="4">
+      <c r="A25" t="s">
+        <v>3</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="D25" s="3"/>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>3</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D26" s="3"/>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>3</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D27" s="3"/>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>3</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="D28" s="3"/>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>3</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D29" s="3"/>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>3</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D30" s="3"/>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>3</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D31" s="3"/>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>3</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D32" s="3"/>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>3</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D33" s="3"/>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>3</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C34" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D25" s="3"/>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="C26" s="4">
-        <v>7</v>
-      </c>
-      <c r="D26" s="3"/>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C27" s="4">
-        <v>7</v>
-      </c>
-      <c r="D27" s="3"/>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="C28" s="4">
-        <v>7</v>
-      </c>
-      <c r="D28" s="3"/>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C29" s="4">
-        <v>12</v>
-      </c>
-      <c r="D29" s="3"/>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="C30" s="4">
-        <v>7</v>
-      </c>
-      <c r="D30" s="3"/>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="C31" s="4">
-        <v>3</v>
-      </c>
-      <c r="D31" s="3"/>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="C32" s="4">
-        <v>5</v>
-      </c>
-      <c r="D32" s="3"/>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="C33" s="4">
-        <v>43</v>
-      </c>
-      <c r="D33" s="3"/>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C34" s="4">
-        <v>8</v>
-      </c>
       <c r="D34" s="3"/>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="C35" s="4">
-        <v>15</v>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>3</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>21</v>
       </c>
       <c r="D35" s="3"/>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="C36" s="4">
-        <v>11</v>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>3</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="D36" s="3"/>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B37" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="C37" s="4">
-        <v>5</v>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>3</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>93</v>
       </c>
       <c r="D37" s="3"/>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B38" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C38" s="4">
-        <v>4</v>
+      <c r="F37" s="3"/>
+      <c r="G37" s="4"/>
+      <c r="H37" s="4"/>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>3</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>94</v>
       </c>
       <c r="D38" s="3"/>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F38" s="3"/>
+      <c r="G38" s="4"/>
+      <c r="H38" s="4"/>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C39" s="1">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+        <v>95</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G39" s="1"/>
+      <c r="H39" s="1"/>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C40" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+        <v>96</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="G40" s="1"/>
+      <c r="H40" s="1"/>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>40</v>
       </c>
@@ -1109,704 +1171,897 @@
         <v>41</v>
       </c>
       <c r="C41" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+      <c r="G41" s="1"/>
+      <c r="H41" s="1"/>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>40</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C42" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+      <c r="G42" s="1"/>
+      <c r="H42" s="1"/>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>40</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C43" s="1">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+      <c r="G43" s="1"/>
+      <c r="H43" s="1"/>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>40</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C44" s="1">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+      <c r="G44" s="1"/>
+      <c r="H44" s="1"/>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>40</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C45" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+      <c r="G45" s="1"/>
+      <c r="H45" s="1"/>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>40</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="C46" s="1">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="G46" s="1"/>
+      <c r="H46" s="1"/>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>40</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="C47" s="1">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="G47" s="1"/>
+      <c r="H47" s="1"/>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>40</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="C48" s="1">
         <v>4</v>
       </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="G48" s="1"/>
+      <c r="H48" s="1"/>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>40</v>
       </c>
       <c r="B49" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C49" s="1">
+        <v>5</v>
+      </c>
+      <c r="G49" s="1"/>
+      <c r="H49" s="1"/>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>40</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C50" s="1">
+        <v>28</v>
+      </c>
+      <c r="G50" s="1"/>
+      <c r="H50" s="1"/>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>40</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C51" s="1">
+        <v>24</v>
+      </c>
+      <c r="G51" s="1"/>
+      <c r="H51" s="1"/>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>40</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C52" s="1">
+        <v>38</v>
+      </c>
+      <c r="G52" s="1"/>
+      <c r="H52" s="1"/>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>40</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C53" s="1">
+        <v>36</v>
+      </c>
+      <c r="G53" s="1"/>
+      <c r="H53" s="1"/>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>40</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C54" s="1">
+        <v>32</v>
+      </c>
+      <c r="G54" s="1"/>
+      <c r="H54" s="1"/>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>40</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C55" s="1">
+        <v>13</v>
+      </c>
+      <c r="G55" s="1"/>
+      <c r="H55" s="1"/>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>40</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C56" s="1">
+        <v>13</v>
+      </c>
+      <c r="G56" s="1"/>
+      <c r="H56" s="1"/>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>40</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C57" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>40</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C58" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>40</v>
+      </c>
+      <c r="B59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C49" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>40</v>
-      </c>
-      <c r="B50" s="1" t="s">
+      <c r="C59" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>40</v>
+      </c>
+      <c r="B60" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C50" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>40</v>
-      </c>
-      <c r="B51" s="1" t="s">
+      <c r="C60" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>40</v>
+      </c>
+      <c r="B61" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C51" s="1">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>40</v>
-      </c>
-      <c r="B52" s="1" t="s">
+      <c r="C61" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>40</v>
+      </c>
+      <c r="B62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C52" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>40</v>
-      </c>
-      <c r="B53" s="1" t="s">
+      <c r="C62" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>40</v>
+      </c>
+      <c r="B63" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C53" s="1">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>40</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C54" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>40</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C55" s="1">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>40</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C56" s="1">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
-        <v>59</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="C57" s="1">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>59</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="C58" s="1">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>59</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C59" s="1">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>59</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C60" s="1">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>59</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C61" s="1">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
-        <v>59</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="C62" s="1">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>59</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>61</v>
-      </c>
       <c r="C63" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="C64" s="1">
-        <v>4</v>
+        <v>40</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="C65" s="1">
-        <v>5</v>
+        <v>50</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
+        <v>40</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C66" s="1">
         <v>59</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="C66" s="1">
-        <v>28</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="C67" s="1">
-        <v>24</v>
+        <v>13</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C68" s="1">
-        <v>38</v>
+        <v>8</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
+        <v>40</v>
+      </c>
+      <c r="B69" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B69" s="1" t="s">
-        <v>67</v>
-      </c>
       <c r="C69" s="1">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C70" s="1">
-        <v>32</v>
+        <v>16</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="C71" s="1">
-        <v>13</v>
+        <v>26</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="C72" s="1">
-        <v>13</v>
+        <v>20</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="C73" s="1">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="C74" s="1">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="B75" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C75" s="1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B76" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C76" s="4">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B77" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="C77" s="4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B78" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C78" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B79" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C79" s="4">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B80" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C80" s="4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B81" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C81" s="4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B82" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="C82" s="4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B83" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C83" s="4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A84" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B84" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C84" s="4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B85" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C85" s="4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B86" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C86" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A87" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B87" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C87" s="4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A88" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B88" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="C88" s="4">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A89" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B89" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C89" s="4">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A90" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B90" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C90" s="4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A91" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B91" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C91" s="4">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A92" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C92" s="6">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A93" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C93" s="6">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A94" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C94" s="6">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A95" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C95" s="6">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A96" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C96" s="6">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C97" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C98" s="6">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A99" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C99" s="6">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B100" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C75" s="1">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
-        <v>59</v>
-      </c>
-      <c r="B76" s="1" t="s">
+      <c r="C100" s="6">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A101" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C101" s="6">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A102" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C102" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A103" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C103" s="6">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A104" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B104" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="C76" s="1">
+      <c r="C104" s="6">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A105" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C105" s="6">
         <v>5</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
-        <v>59</v>
-      </c>
-      <c r="B77" s="1" t="s">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A106" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C106" s="6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A107" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C107" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A108" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C108" s="6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A109" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C109" s="6">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A110" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B110" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="C77" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
-        <v>59</v>
-      </c>
-      <c r="B78" s="1" t="s">
+      <c r="C110" s="6">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A111" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C111" s="6">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A112" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B112" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="C78" s="1">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A79" t="s">
-        <v>59</v>
-      </c>
-      <c r="B79" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="C79" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A80" t="s">
-        <v>59</v>
-      </c>
-      <c r="B80" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="C80" s="1">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
-        <v>59</v>
-      </c>
-      <c r="B81" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="C81" s="1">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
-        <v>59</v>
-      </c>
-      <c r="B82" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="C82" s="1">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A83" t="s">
-        <v>59</v>
-      </c>
-      <c r="B83" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="C83" s="1">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A84" t="s">
-        <v>59</v>
-      </c>
-      <c r="B84" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="C84" s="1">
+      <c r="C112" s="6">
         <v>8</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A85" t="s">
-        <v>59</v>
-      </c>
-      <c r="B85" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="C85" s="1">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A86" t="s">
-        <v>59</v>
-      </c>
-      <c r="B86" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="C86" s="1">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A87" t="s">
-        <v>59</v>
-      </c>
-      <c r="B87" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="C87" s="1">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A88" t="s">
-        <v>59</v>
-      </c>
-      <c r="B88" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="C88" s="1">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A89" t="s">
-        <v>59</v>
-      </c>
-      <c r="B89" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="C89" s="1">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A90" t="s">
-        <v>59</v>
-      </c>
-      <c r="B90" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="C90" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A91" t="s">
-        <v>59</v>
-      </c>
-      <c r="B91" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="C91" s="1">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B92" s="1"/>
-      <c r="C92" s="1"/>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B93" s="1"/>
-      <c r="C93" s="1"/>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B94" s="1"/>
-      <c r="C94" s="1"/>
-    </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B95" s="1"/>
-      <c r="C95" s="1"/>
-    </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B96" s="1"/>
-      <c r="C96" s="1"/>
-    </row>
-    <row r="97" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B97" s="1"/>
-      <c r="C97" s="1"/>
-    </row>
-    <row r="98" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B98" s="1"/>
-      <c r="C98" s="1"/>
-    </row>
-    <row r="99" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B99" s="1"/>
-      <c r="C99" s="1"/>
-    </row>
-    <row r="100" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B100" s="1"/>
-      <c r="C100" s="1"/>
-    </row>
-    <row r="101" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B101" s="1"/>
-      <c r="C101" s="1"/>
-    </row>
-    <row r="102" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B102" s="1"/>
-      <c r="C102" s="1"/>
-    </row>
-    <row r="103" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B103" s="1"/>
-      <c r="C103" s="1"/>
-    </row>
-    <row r="104" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B104" s="1"/>
-      <c r="C104" s="1"/>
-    </row>
-    <row r="105" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B105" s="1"/>
-      <c r="C105" s="1"/>
-    </row>
-    <row r="106" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B106" s="1"/>
-      <c r="C106" s="1"/>
-    </row>
-    <row r="107" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B107" s="1"/>
-      <c r="C107" s="1"/>
-    </row>
-    <row r="108" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B108" s="1"/>
-      <c r="C108" s="1"/>
-    </row>
-    <row r="109" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B109" s="1"/>
-      <c r="C109" s="1"/>
-    </row>
-    <row r="110" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B110" s="1"/>
-      <c r="C110" s="1"/>
-    </row>
-    <row r="111" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B111" s="1"/>
-      <c r="C111" s="1"/>
-    </row>
-    <row r="112" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B112" s="1"/>
-      <c r="C112" s="1"/>
-    </row>
-    <row r="113" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B113" s="1"/>
-      <c r="C113" s="1"/>
-    </row>
-    <row r="114" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B114" s="1"/>
-      <c r="C114" s="1"/>
-    </row>
-    <row r="115" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A113" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C113" s="6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A114" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C114" s="6">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B115" s="1"/>
       <c r="C115" s="1"/>
     </row>
-    <row r="116" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B116" s="1"/>
       <c r="C116" s="1"/>
     </row>
-    <row r="117" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B117" s="1"/>
       <c r="C117" s="1"/>
     </row>
-    <row r="118" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B118" s="1"/>
       <c r="C118" s="1"/>
     </row>
-    <row r="119" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B119" s="1"/>
       <c r="C119" s="1"/>
     </row>
-    <row r="120" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B120" s="1"/>
       <c r="C120" s="1"/>
     </row>
-    <row r="121" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B121" s="1"/>
       <c r="C121" s="1"/>
     </row>
-    <row r="122" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B122" s="1"/>
       <c r="C122" s="1"/>
     </row>
-    <row r="123" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B123" s="1"/>
       <c r="C123" s="1"/>
     </row>
-    <row r="124" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B124" s="1"/>
       <c r="C124" s="1"/>
     </row>
-    <row r="125" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B125" s="1"/>
       <c r="C125" s="1"/>
     </row>
-    <row r="126" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B126" s="1"/>
       <c r="C126" s="1"/>
     </row>
-    <row r="127" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B127" s="1"/>
       <c r="C127" s="1"/>
     </row>
-    <row r="128" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B128" s="1"/>
       <c r="C128" s="1"/>
     </row>

--- a/addresses/good_addresses.xlsx
+++ b/addresses/good_addresses.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="113">
   <si>
     <t>City</t>
   </si>
@@ -313,6 +313,51 @@
   </si>
   <si>
     <t>40</t>
+  </si>
+  <si>
+    <t>מרומי שדה</t>
+  </si>
+  <si>
+    <t>רשבם</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>חפץ חיים</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>107</t>
+  </si>
+  <si>
+    <t>99</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>59</t>
+  </si>
+  <si>
+    <t>38</t>
+  </si>
+  <si>
+    <t>44</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>אשר לשלמה</t>
+  </si>
+  <si>
+    <t>required_delivery_date</t>
   </si>
 </sst>
 </file>
@@ -336,7 +381,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -349,8 +394,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.749992370372631"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -358,11 +409,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -379,6 +445,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -682,12 +754,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H261"/>
+  <dimension ref="A1:H260"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.8984375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17.59765625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.3984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.3984375" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="17.69921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -701,7 +774,9 @@
       <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2"/>
+      <c r="D1" s="7" t="s">
+        <v>112</v>
+      </c>
       <c r="E1" s="2"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -714,6 +789,9 @@
       <c r="C2" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="D2" s="8">
+        <v>45966</v>
+      </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
@@ -725,6 +803,9 @@
       <c r="C3" s="1" t="s">
         <v>7</v>
       </c>
+      <c r="D3" s="8">
+        <v>45966</v>
+      </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
@@ -736,6 +817,9 @@
       <c r="C4" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="D4" s="8">
+        <v>45966</v>
+      </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
@@ -747,6 +831,9 @@
       <c r="C5" s="1" t="s">
         <v>11</v>
       </c>
+      <c r="D5" s="8">
+        <v>45966</v>
+      </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
@@ -758,6 +845,9 @@
       <c r="C6" s="1" t="s">
         <v>13</v>
       </c>
+      <c r="D6" s="8">
+        <v>45966</v>
+      </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
@@ -769,6 +859,9 @@
       <c r="C7" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="D7" s="8">
+        <v>45966</v>
+      </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
@@ -780,6 +873,9 @@
       <c r="C8" s="1" t="s">
         <v>16</v>
       </c>
+      <c r="D8" s="8">
+        <v>45966</v>
+      </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
@@ -791,6 +887,9 @@
       <c r="C9" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="D9" s="8">
+        <v>45966</v>
+      </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
@@ -802,6 +901,9 @@
       <c r="C10" s="1" t="s">
         <v>19</v>
       </c>
+      <c r="D10" s="8">
+        <v>45966</v>
+      </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
@@ -813,6 +915,9 @@
       <c r="C11" s="1" t="s">
         <v>21</v>
       </c>
+      <c r="D11" s="8">
+        <v>45966</v>
+      </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
@@ -824,6 +929,9 @@
       <c r="C12" s="1" t="s">
         <v>13</v>
       </c>
+      <c r="D12" s="8">
+        <v>45966</v>
+      </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
@@ -835,6 +943,9 @@
       <c r="C13" s="1" t="s">
         <v>21</v>
       </c>
+      <c r="D13" s="8">
+        <v>45966</v>
+      </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
@@ -846,6 +957,9 @@
       <c r="C14" s="1" t="s">
         <v>25</v>
       </c>
+      <c r="D14" s="8">
+        <v>45966</v>
+      </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
@@ -857,6 +971,9 @@
       <c r="C15" s="1" t="s">
         <v>26</v>
       </c>
+      <c r="D15" s="8">
+        <v>45966</v>
+      </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
@@ -868,6 +985,9 @@
       <c r="C16" s="1" t="s">
         <v>27</v>
       </c>
+      <c r="D16" s="8">
+        <v>45966</v>
+      </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
@@ -879,6 +999,9 @@
       <c r="C17" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="D17" s="8">
+        <v>45966</v>
+      </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
@@ -890,6 +1013,9 @@
       <c r="C18" s="1" t="s">
         <v>28</v>
       </c>
+      <c r="D18" s="8">
+        <v>45966</v>
+      </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
@@ -901,7 +1027,9 @@
       <c r="C19" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D19" s="3"/>
+      <c r="D19" s="8">
+        <v>45966</v>
+      </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
@@ -913,7 +1041,9 @@
       <c r="C20" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D20" s="3"/>
+      <c r="D20" s="8">
+        <v>45966</v>
+      </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
@@ -925,7 +1055,9 @@
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D21" s="3"/>
+      <c r="D21" s="8">
+        <v>45966</v>
+      </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
@@ -937,7 +1069,9 @@
       <c r="C22" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="D22" s="3"/>
+      <c r="D22" s="8">
+        <v>45966</v>
+      </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
@@ -949,7 +1083,9 @@
       <c r="C23" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D23" s="3"/>
+      <c r="D23" s="8">
+        <v>45966</v>
+      </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
@@ -961,7 +1097,9 @@
       <c r="C24" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D24" s="3"/>
+      <c r="D24" s="8">
+        <v>45966</v>
+      </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
@@ -973,7 +1111,9 @@
       <c r="C25" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="D25" s="3"/>
+      <c r="D25" s="8">
+        <v>45966</v>
+      </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
@@ -985,7 +1125,9 @@
       <c r="C26" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D26" s="3"/>
+      <c r="D26" s="8">
+        <v>45966</v>
+      </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
@@ -997,7 +1139,9 @@
       <c r="C27" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="D27" s="3"/>
+      <c r="D27" s="8">
+        <v>45966</v>
+      </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
@@ -1009,7 +1153,9 @@
       <c r="C28" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="D28" s="3"/>
+      <c r="D28" s="8">
+        <v>45966</v>
+      </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
@@ -1021,7 +1167,9 @@
       <c r="C29" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="D29" s="3"/>
+      <c r="D29" s="8">
+        <v>45966</v>
+      </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
@@ -1033,7 +1181,9 @@
       <c r="C30" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D30" s="3"/>
+      <c r="D30" s="8">
+        <v>45966</v>
+      </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
@@ -1045,7 +1195,9 @@
       <c r="C31" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="D31" s="3"/>
+      <c r="D31" s="8">
+        <v>45966</v>
+      </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
@@ -1057,7 +1209,9 @@
       <c r="C32" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D32" s="3"/>
+      <c r="D32" s="8">
+        <v>45966</v>
+      </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
@@ -1069,7 +1223,9 @@
       <c r="C33" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D33" s="3"/>
+      <c r="D33" s="8">
+        <v>45966</v>
+      </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
@@ -1081,7 +1237,9 @@
       <c r="C34" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D34" s="3"/>
+      <c r="D34" s="8">
+        <v>45966</v>
+      </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
@@ -1093,7 +1251,9 @@
       <c r="C35" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D35" s="3"/>
+      <c r="D35" s="8">
+        <v>45966</v>
+      </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
@@ -1105,7 +1265,9 @@
       <c r="C36" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D36" s="3"/>
+      <c r="D36" s="8">
+        <v>45966</v>
+      </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
@@ -1117,7 +1279,9 @@
       <c r="C37" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="D37" s="3"/>
+      <c r="D37" s="8">
+        <v>45966</v>
+      </c>
       <c r="F37" s="3"/>
       <c r="G37" s="4"/>
       <c r="H37" s="4"/>
@@ -1132,7 +1296,9 @@
       <c r="C38" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="D38" s="3"/>
+      <c r="D38" s="8">
+        <v>45966</v>
+      </c>
       <c r="F38" s="3"/>
       <c r="G38" s="4"/>
       <c r="H38" s="4"/>
@@ -1147,6 +1313,9 @@
       <c r="C39" s="1" t="s">
         <v>28</v>
       </c>
+      <c r="D39" s="8">
+        <v>45966</v>
+      </c>
       <c r="G39" s="1"/>
       <c r="H39" s="1"/>
     </row>
@@ -1160,1444 +1329,1807 @@
       <c r="C40" s="1" t="s">
         <v>97</v>
       </c>
+      <c r="D40" s="8">
+        <v>45966</v>
+      </c>
       <c r="G40" s="1"/>
       <c r="H40" s="1"/>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C41" s="1">
-        <v>38</v>
-      </c>
-      <c r="G41" s="1"/>
-      <c r="H41" s="1"/>
+        <v>95</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D41" s="8">
+        <v>45966</v>
+      </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C42" s="1">
-        <v>38</v>
-      </c>
-      <c r="G42" s="1"/>
-      <c r="H42" s="1"/>
+        <v>85</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D42" s="8">
+        <v>45966</v>
+      </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C43" s="1">
-        <v>47</v>
-      </c>
-      <c r="G43" s="1"/>
-      <c r="H43" s="1"/>
+        <v>98</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D43" s="8">
+        <v>45966</v>
+      </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C44" s="1">
-        <v>37</v>
-      </c>
-      <c r="G44" s="1"/>
-      <c r="H44" s="1"/>
+        <v>99</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D44" s="8">
+        <v>45966</v>
+      </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C45" s="1">
-        <v>37</v>
-      </c>
-      <c r="G45" s="1"/>
-      <c r="H45" s="1"/>
+        <v>77</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D45" s="8">
+        <v>45966</v>
+      </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C46" s="1">
-        <v>17</v>
-      </c>
-      <c r="G46" s="1"/>
-      <c r="H46" s="1"/>
+        <v>92</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D46" s="8">
+        <v>45966</v>
+      </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C47" s="1">
-        <v>1</v>
-      </c>
-      <c r="G47" s="1"/>
-      <c r="H47" s="1"/>
+        <v>6</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D47" s="8">
+        <v>45966</v>
+      </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="B48" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D48" s="8">
+        <v>45966</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>3</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D49" s="8">
+        <v>45966</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>3</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D50" s="8">
+        <v>45966</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>3</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D51" s="8">
+        <v>45966</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>3</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="D52" s="8">
+        <v>45966</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>3</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D53" s="8">
+        <v>45966</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>3</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="D54" s="8">
+        <v>45966</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>3</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="D55" s="8">
+        <v>45966</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>3</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="D56" s="8">
+        <v>45966</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>3</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="D57" s="8">
+        <v>45966</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>3</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D58" s="8">
+        <v>45966</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>3</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="D59" s="8">
+        <v>45966</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>3</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="D60" s="8">
+        <v>45966</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>3</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D61" s="8">
+        <v>45966</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>3</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="D62" s="8">
+        <v>45966</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>3</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D63" s="8">
+        <v>45966</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>3</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D64" s="8">
+        <v>45966</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>3</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D65" s="8">
+        <v>45966</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>3</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="D66" s="8">
+        <v>45966</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>3</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D67" s="8">
+        <v>45966</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>3</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="D68" s="8">
+        <v>45966</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>3</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D69" s="8">
+        <v>45966</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>40</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C70" s="1">
+        <v>38</v>
+      </c>
+      <c r="D70" s="8">
+        <v>45966</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>40</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C71" s="1">
+        <v>38</v>
+      </c>
+      <c r="D71" s="8">
+        <v>45966</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>40</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C72" s="1">
+        <v>47</v>
+      </c>
+      <c r="D72" s="8">
+        <v>45966</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>40</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C73" s="1">
+        <v>37</v>
+      </c>
+      <c r="D73" s="8">
+        <v>45966</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>40</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C74" s="1">
+        <v>37</v>
+      </c>
+      <c r="D74" s="8">
+        <v>45966</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>40</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C75" s="1">
+        <v>17</v>
+      </c>
+      <c r="D75" s="8">
+        <v>45966</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>40</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C76" s="1">
+        <v>1</v>
+      </c>
+      <c r="D76" s="8">
+        <v>45966</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>40</v>
+      </c>
+      <c r="B77" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C48" s="1">
+      <c r="C77" s="1">
         <v>4</v>
       </c>
-      <c r="G48" s="1"/>
-      <c r="H48" s="1"/>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>40</v>
-      </c>
-      <c r="B49" s="1" t="s">
+      <c r="D77" s="8">
+        <v>45966</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>40</v>
+      </c>
+      <c r="B78" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C49" s="1">
+      <c r="C78" s="1">
         <v>5</v>
       </c>
-      <c r="G49" s="1"/>
-      <c r="H49" s="1"/>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>40</v>
-      </c>
-      <c r="B50" s="1" t="s">
+      <c r="D78" s="8">
+        <v>45966</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>40</v>
+      </c>
+      <c r="B79" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C50" s="1">
+      <c r="C79" s="1">
         <v>28</v>
       </c>
-      <c r="G50" s="1"/>
-      <c r="H50" s="1"/>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>40</v>
-      </c>
-      <c r="B51" s="1" t="s">
+      <c r="D79" s="8">
+        <v>45966</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>40</v>
+      </c>
+      <c r="B80" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C51" s="1">
+      <c r="C80" s="1">
         <v>24</v>
       </c>
-      <c r="G51" s="1"/>
-      <c r="H51" s="1"/>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>40</v>
-      </c>
-      <c r="B52" s="1" t="s">
+      <c r="D80" s="8">
+        <v>45966</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>40</v>
+      </c>
+      <c r="B81" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C52" s="1">
+      <c r="C81" s="1">
         <v>38</v>
       </c>
-      <c r="G52" s="1"/>
-      <c r="H52" s="1"/>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>40</v>
-      </c>
-      <c r="B53" s="1" t="s">
+      <c r="D81" s="8">
+        <v>45966</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>40</v>
+      </c>
+      <c r="B82" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C53" s="1">
+      <c r="C82" s="1">
         <v>36</v>
       </c>
-      <c r="G53" s="1"/>
-      <c r="H53" s="1"/>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>40</v>
-      </c>
-      <c r="B54" s="1" t="s">
+      <c r="D82" s="8">
+        <v>45966</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>40</v>
+      </c>
+      <c r="B83" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C54" s="1">
+      <c r="C83" s="1">
         <v>32</v>
       </c>
-      <c r="G54" s="1"/>
-      <c r="H54" s="1"/>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>40</v>
-      </c>
-      <c r="B55" s="1" t="s">
+      <c r="D83" s="8">
+        <v>45966</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>40</v>
+      </c>
+      <c r="B84" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C55" s="1">
+      <c r="C84" s="1">
         <v>13</v>
       </c>
-      <c r="G55" s="1"/>
-      <c r="H55" s="1"/>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>40</v>
-      </c>
-      <c r="B56" s="1" t="s">
+      <c r="D84" s="8">
+        <v>45966</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>40</v>
+      </c>
+      <c r="B85" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C56" s="1">
+      <c r="C85" s="1">
         <v>13</v>
       </c>
-      <c r="G56" s="1"/>
-      <c r="H56" s="1"/>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
-        <v>40</v>
-      </c>
-      <c r="B57" s="1" t="s">
+      <c r="D85" s="8">
+        <v>45966</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>40</v>
+      </c>
+      <c r="B86" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C57" s="1">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>40</v>
-      </c>
-      <c r="B58" s="1" t="s">
+      <c r="C86" s="1">
+        <v>30</v>
+      </c>
+      <c r="D86" s="8">
+        <v>45966</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>40</v>
+      </c>
+      <c r="B87" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C58" s="1">
+      <c r="C87" s="1">
         <v>4</v>
       </c>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>40</v>
-      </c>
-      <c r="B59" s="1" t="s">
+      <c r="D87" s="8">
+        <v>45966</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>40</v>
+      </c>
+      <c r="B88" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C59" s="1">
+      <c r="C88" s="1">
         <v>6</v>
       </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>40</v>
-      </c>
-      <c r="B60" s="1" t="s">
+      <c r="D88" s="8">
+        <v>45966</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>40</v>
+      </c>
+      <c r="B89" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C60" s="1">
+      <c r="C89" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>40</v>
-      </c>
-      <c r="B61" s="1" t="s">
+      <c r="D89" s="8">
+        <v>45966</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>40</v>
+      </c>
+      <c r="B90" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C61" s="1">
+      <c r="C90" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
-        <v>40</v>
-      </c>
-      <c r="B62" s="1" t="s">
+      <c r="D90" s="8">
+        <v>45966</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>40</v>
+      </c>
+      <c r="B91" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C62" s="1">
+      <c r="C91" s="1">
         <v>13</v>
       </c>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>40</v>
-      </c>
-      <c r="B63" s="1" t="s">
+      <c r="D91" s="8">
+        <v>45966</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>40</v>
+      </c>
+      <c r="B92" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C63" s="1">
+      <c r="C92" s="1">
         <v>14</v>
       </c>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
-        <v>40</v>
-      </c>
-      <c r="B64" s="1" t="s">
+      <c r="D92" s="8">
+        <v>45966</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>40</v>
+      </c>
+      <c r="B93" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C64" s="1">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
-        <v>40</v>
-      </c>
-      <c r="B65" s="1" t="s">
+      <c r="C93" s="1">
+        <v>40</v>
+      </c>
+      <c r="D93" s="8">
+        <v>45966</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>40</v>
+      </c>
+      <c r="B94" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C65" s="1">
+      <c r="C94" s="1">
         <v>50</v>
       </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
-        <v>40</v>
-      </c>
-      <c r="B66" s="1" t="s">
+      <c r="D94" s="8">
+        <v>45966</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>40</v>
+      </c>
+      <c r="B95" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C66" s="1">
+      <c r="C95" s="1">
         <v>59</v>
       </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
-        <v>40</v>
-      </c>
-      <c r="B67" s="1" t="s">
+      <c r="D95" s="8">
+        <v>45966</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>40</v>
+      </c>
+      <c r="B96" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C67" s="1">
+      <c r="C96" s="1">
         <v>13</v>
       </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
-        <v>40</v>
-      </c>
-      <c r="B68" s="1" t="s">
+      <c r="D96" s="8">
+        <v>45966</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>40</v>
+      </c>
+      <c r="B97" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C68" s="1">
+      <c r="C97" s="1">
         <v>8</v>
       </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
-        <v>40</v>
-      </c>
-      <c r="B69" s="1" t="s">
+      <c r="D97" s="8">
+        <v>45966</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>40</v>
+      </c>
+      <c r="B98" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="C69" s="1">
+      <c r="C98" s="1">
         <v>15</v>
       </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
-        <v>40</v>
-      </c>
-      <c r="B70" s="1" t="s">
+      <c r="D98" s="8">
+        <v>45966</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>40</v>
+      </c>
+      <c r="B99" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C70" s="1">
+      <c r="C99" s="1">
         <v>16</v>
       </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
-        <v>40</v>
-      </c>
-      <c r="B71" s="1" t="s">
+      <c r="D99" s="8">
+        <v>45966</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>40</v>
+      </c>
+      <c r="B100" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="C71" s="1">
+      <c r="C100" s="1">
         <v>26</v>
       </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
-        <v>40</v>
-      </c>
-      <c r="B72" s="1" t="s">
+      <c r="D100" s="8">
+        <v>45966</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>40</v>
+      </c>
+      <c r="B101" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C72" s="1">
+      <c r="C101" s="1">
         <v>20</v>
       </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
-        <v>40</v>
-      </c>
-      <c r="B73" s="1" t="s">
+      <c r="D101" s="8">
+        <v>45966</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>40</v>
+      </c>
+      <c r="B102" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="C73" s="1">
+      <c r="C102" s="1">
         <v>31</v>
       </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
-        <v>40</v>
-      </c>
-      <c r="B74" s="1" t="s">
+      <c r="D102" s="8">
+        <v>45966</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>40</v>
+      </c>
+      <c r="B103" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C74" s="1">
+      <c r="C103" s="1">
         <v>14</v>
       </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
-        <v>40</v>
-      </c>
-      <c r="B75" s="1" t="s">
+      <c r="D103" s="8">
+        <v>45966</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>40</v>
+      </c>
+      <c r="B104" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C75" s="1">
+      <c r="C104" s="1">
         <v>12</v>
       </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A76" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B76" s="5" t="s">
+      <c r="D104" s="8">
+        <v>45966</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A105" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B105" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C76" s="4">
+      <c r="C105" s="4">
         <v>46</v>
       </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A77" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B77" s="5" t="s">
+      <c r="D105" s="8">
+        <v>45966</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A106" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B106" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="C77" s="4">
+      <c r="C106" s="4">
         <v>6</v>
       </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A78" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B78" s="5" t="s">
+      <c r="D106" s="8">
+        <v>45966</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A107" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B107" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="C78" s="4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A79" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B79" s="5" t="s">
+      <c r="C107" s="4">
+        <v>3</v>
+      </c>
+      <c r="D107" s="8">
+        <v>45966</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A108" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B108" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C79" s="4">
+      <c r="C108" s="4">
         <v>8</v>
       </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A80" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B80" s="5" t="s">
+      <c r="D108" s="8">
+        <v>45966</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A109" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B109" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="C80" s="4">
+      <c r="C109" s="4">
         <v>5</v>
       </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A81" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B81" s="5" t="s">
+      <c r="D109" s="8">
+        <v>45966</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A110" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B110" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="C81" s="4">
+      <c r="C110" s="4">
         <v>7</v>
       </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A82" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B82" s="5" t="s">
+      <c r="D110" s="8">
+        <v>45966</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A111" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B111" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="C82" s="4">
+      <c r="C111" s="4">
         <v>7</v>
       </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A83" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B83" s="5" t="s">
+      <c r="D111" s="8">
+        <v>45966</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A112" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B112" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="C83" s="4">
+      <c r="C112" s="4">
         <v>7</v>
       </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A84" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B84" s="5" t="s">
+      <c r="D112" s="8">
+        <v>45966</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A113" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B113" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C84" s="4">
+      <c r="C113" s="4">
         <v>12</v>
       </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A85" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B85" s="5" t="s">
+      <c r="D113" s="8">
+        <v>45996</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A114" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B114" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="C85" s="4">
+      <c r="C114" s="4">
         <v>7</v>
       </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A86" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B86" s="5" t="s">
+      <c r="D114" s="8">
+        <v>45996</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A115" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B115" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C86" s="4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A87" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B87" s="5" t="s">
+      <c r="C115" s="4">
+        <v>3</v>
+      </c>
+      <c r="D115" s="8">
+        <v>45996</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A116" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B116" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="C87" s="4">
+      <c r="C116" s="4">
         <v>5</v>
       </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A88" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B88" s="5" t="s">
+      <c r="D116" s="8">
+        <v>45996</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A117" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B117" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="C88" s="4">
+      <c r="C117" s="4">
         <v>43</v>
       </c>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A89" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B89" s="5" t="s">
+      <c r="D117" s="8">
+        <v>45996</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A118" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B118" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="C89" s="4">
+      <c r="C118" s="4">
         <v>8</v>
       </c>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A90" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B90" s="5" t="s">
+      <c r="D118" s="8">
+        <v>45996</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A119" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B119" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="C90" s="4">
+      <c r="C119" s="4">
         <v>15</v>
       </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A91" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B91" s="5" t="s">
+      <c r="D119" s="8">
+        <v>45996</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A120" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B120" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="C91" s="4">
+      <c r="C120" s="4">
         <v>11</v>
       </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A92" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B92" s="1" t="s">
+      <c r="D120" s="8">
+        <v>45996</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A121" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B121" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="C92" s="6">
+      <c r="C121" s="6">
         <v>12</v>
       </c>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A93" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B93" s="1" t="s">
+      <c r="D121" s="8">
+        <v>45996</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A122" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B122" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C93" s="6">
+      <c r="C122" s="6">
         <v>9</v>
       </c>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A94" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B94" s="1" t="s">
+      <c r="D122" s="8">
+        <v>45996</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A123" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B123" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C94" s="6">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A95" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B95" s="1" t="s">
+      <c r="C123" s="6">
+        <v>30</v>
+      </c>
+      <c r="D123" s="8">
+        <v>45996</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A124" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B124" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="C95" s="6">
+      <c r="C124" s="6">
         <v>9</v>
       </c>
-    </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A96" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B96" s="1" t="s">
+      <c r="D124" s="8">
+        <v>45996</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A125" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B125" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C96" s="6">
+      <c r="C125" s="6">
         <v>16</v>
       </c>
-    </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A97" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B97" s="1" t="s">
+      <c r="D125" s="8">
+        <v>45996</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A126" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B126" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C97" s="6">
+      <c r="C126" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A98" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B98" s="1" t="s">
+      <c r="D126" s="8">
+        <v>45996</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A127" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B127" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C98" s="6">
+      <c r="C127" s="6">
         <v>21</v>
       </c>
-    </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A99" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B99" s="1" t="s">
+      <c r="D127" s="8">
+        <v>45996</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A128" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B128" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C99" s="6">
+      <c r="C128" s="6">
         <v>32</v>
       </c>
-    </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A100" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B100" s="1" t="s">
+      <c r="D128" s="8">
+        <v>45694</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A129" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B129" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C100" s="6">
+      <c r="C129" s="6">
         <v>25</v>
       </c>
-    </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A101" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B101" s="1" t="s">
+      <c r="D129" s="8">
+        <v>45694</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A130" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B130" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C101" s="6">
+      <c r="C130" s="6">
         <v>20</v>
       </c>
-    </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A102" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B102" s="1" t="s">
+      <c r="D130" s="8">
+        <v>45694</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A131" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B131" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C102" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A103" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B103" s="1" t="s">
+      <c r="C131" s="6">
+        <v>3</v>
+      </c>
+      <c r="D131" s="8">
+        <v>45694</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A132" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B132" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C103" s="6">
+      <c r="C132" s="6">
         <v>21</v>
       </c>
-    </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A104" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B104" s="1" t="s">
+      <c r="D132" s="8">
+        <v>45694</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A133" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B133" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="C104" s="6">
+      <c r="C133" s="6">
         <v>19</v>
       </c>
-    </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A105" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B105" s="1" t="s">
+      <c r="D133" s="8">
+        <v>45694</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A134" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B134" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C105" s="6">
+      <c r="C134" s="6">
         <v>5</v>
       </c>
-    </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A106" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B106" s="1" t="s">
+      <c r="D134" s="8">
+        <v>45694</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A135" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B135" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C106" s="6">
+      <c r="C135" s="6">
         <v>7</v>
       </c>
-    </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A107" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B107" s="1" t="s">
+      <c r="D135" s="8">
+        <v>45694</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A136" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B136" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C107" s="6">
+      <c r="C136" s="6">
         <v>10</v>
       </c>
-    </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A108" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B108" s="1" t="s">
+      <c r="D136" s="8">
+        <v>45694</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A137" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B137" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C108" s="6">
+      <c r="C137" s="6">
         <v>4</v>
       </c>
-    </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A109" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B109" s="1" t="s">
+      <c r="D137" s="8">
+        <v>45694</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A138" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B138" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C109" s="6">
+      <c r="C138" s="6">
         <v>9</v>
       </c>
-    </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A110" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B110" s="1" t="s">
+      <c r="D138" s="8">
+        <v>45694</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A139" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B139" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="C110" s="6">
+      <c r="C139" s="6">
         <v>17</v>
       </c>
-    </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A111" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B111" s="1" t="s">
+      <c r="D139" s="8">
+        <v>45694</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A140" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B140" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C111" s="6">
+      <c r="C140" s="6">
         <v>21</v>
       </c>
-    </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A112" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B112" s="1" t="s">
+      <c r="D140" s="8">
+        <v>45694</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A141" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B141" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="C112" s="6">
+      <c r="C141" s="6">
         <v>8</v>
       </c>
-    </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A113" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B113" s="1" t="s">
+      <c r="D141" s="8">
+        <v>45694</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A142" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B142" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="C113" s="6">
+      <c r="C142" s="6">
         <v>7</v>
       </c>
-    </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A114" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B114" s="1" t="s">
+      <c r="D142" s="8">
+        <v>45694</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A143" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B143" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="C114" s="6">
+      <c r="C143" s="6">
         <v>17</v>
       </c>
-    </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B115" s="1"/>
-      <c r="C115" s="1"/>
-    </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B116" s="1"/>
-      <c r="C116" s="1"/>
-    </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B117" s="1"/>
-      <c r="C117" s="1"/>
-    </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B118" s="1"/>
-      <c r="C118" s="1"/>
-    </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B119" s="1"/>
-      <c r="C119" s="1"/>
-    </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B120" s="1"/>
-      <c r="C120" s="1"/>
-    </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B121" s="1"/>
-      <c r="C121" s="1"/>
-    </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B122" s="1"/>
-      <c r="C122" s="1"/>
-    </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B123" s="1"/>
-      <c r="C123" s="1"/>
-    </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B124" s="1"/>
-      <c r="C124" s="1"/>
-    </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B125" s="1"/>
-      <c r="C125" s="1"/>
-    </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B126" s="1"/>
-      <c r="C126" s="1"/>
-    </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B127" s="1"/>
-      <c r="C127" s="1"/>
-    </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B128" s="1"/>
-      <c r="C128" s="1"/>
-    </row>
-    <row r="129" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B129" s="1"/>
-      <c r="C129" s="1"/>
-    </row>
-    <row r="130" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B130" s="1"/>
-      <c r="C130" s="1"/>
-    </row>
-    <row r="131" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B131" s="1"/>
-      <c r="C131" s="1"/>
-    </row>
-    <row r="132" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B132" s="1"/>
-      <c r="C132" s="1"/>
-    </row>
-    <row r="133" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B133" s="1"/>
-      <c r="C133" s="1"/>
-    </row>
-    <row r="134" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B134" s="1"/>
-      <c r="C134" s="1"/>
-    </row>
-    <row r="135" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B135" s="1"/>
-      <c r="C135" s="1"/>
-    </row>
-    <row r="136" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B136" s="1"/>
-      <c r="C136" s="1"/>
-    </row>
-    <row r="137" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B137" s="1"/>
-      <c r="C137" s="1"/>
-    </row>
-    <row r="138" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B138" s="1"/>
-      <c r="C138" s="1"/>
-    </row>
-    <row r="139" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B139" s="1"/>
-      <c r="C139" s="1"/>
-    </row>
-    <row r="140" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B140" s="1"/>
-      <c r="C140" s="1"/>
-    </row>
-    <row r="141" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B141" s="1"/>
-      <c r="C141" s="1"/>
-    </row>
-    <row r="142" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B142" s="1"/>
-      <c r="C142" s="1"/>
-    </row>
-    <row r="143" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B143" s="1"/>
-      <c r="C143" s="1"/>
-    </row>
-    <row r="144" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="D143" s="8">
+        <v>45694</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B144" s="1"/>
-      <c r="C144" s="1"/>
-    </row>
-    <row r="145" spans="2:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="145" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B145" s="1"/>
-      <c r="C145" s="1"/>
-    </row>
-    <row r="146" spans="2:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="146" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B146" s="1"/>
-      <c r="C146" s="1"/>
-    </row>
-    <row r="147" spans="2:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="147" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B147" s="1"/>
-      <c r="C147" s="1"/>
-    </row>
-    <row r="148" spans="2:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="148" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B148" s="1"/>
-      <c r="C148" s="1"/>
-    </row>
-    <row r="149" spans="2:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="149" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B149" s="1"/>
-      <c r="C149" s="1"/>
-    </row>
-    <row r="150" spans="2:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="150" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B150" s="1"/>
-      <c r="C150" s="1"/>
-    </row>
-    <row r="151" spans="2:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="151" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B151" s="1"/>
-      <c r="C151" s="1"/>
-    </row>
-    <row r="152" spans="2:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="152" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B152" s="1"/>
-      <c r="C152" s="1"/>
-    </row>
-    <row r="153" spans="2:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="153" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B153" s="1"/>
-      <c r="C153" s="1"/>
-    </row>
-    <row r="154" spans="2:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="154" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B154" s="1"/>
-      <c r="C154" s="1"/>
-    </row>
-    <row r="155" spans="2:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="155" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B155" s="1"/>
-      <c r="C155" s="1"/>
-    </row>
-    <row r="156" spans="2:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="156" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B156" s="1"/>
-      <c r="C156" s="1"/>
-    </row>
-    <row r="157" spans="2:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="157" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B157" s="1"/>
-      <c r="C157" s="1"/>
-    </row>
-    <row r="158" spans="2:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="158" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B158" s="1"/>
-      <c r="C158" s="1"/>
-    </row>
-    <row r="159" spans="2:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="159" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B159" s="1"/>
-      <c r="C159" s="1"/>
-    </row>
-    <row r="160" spans="2:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="160" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B160" s="1"/>
-      <c r="C160" s="1"/>
-    </row>
-    <row r="161" spans="2:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="161" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B161" s="1"/>
-      <c r="C161" s="1"/>
-    </row>
-    <row r="162" spans="2:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="162" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B162" s="1"/>
-      <c r="C162" s="1"/>
-    </row>
-    <row r="163" spans="2:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="163" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B163" s="1"/>
-      <c r="C163" s="1"/>
-    </row>
-    <row r="164" spans="2:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="164" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B164" s="1"/>
-      <c r="C164" s="1"/>
-    </row>
-    <row r="165" spans="2:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="165" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B165" s="1"/>
-      <c r="C165" s="1"/>
-    </row>
-    <row r="166" spans="2:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="166" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B166" s="1"/>
-      <c r="C166" s="1"/>
-    </row>
-    <row r="167" spans="2:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="167" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B167" s="1"/>
-      <c r="C167" s="1"/>
-    </row>
-    <row r="168" spans="2:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="168" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B168" s="1"/>
-      <c r="C168" s="1"/>
-    </row>
-    <row r="169" spans="2:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="169" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B169" s="1"/>
-      <c r="C169" s="1"/>
-    </row>
-    <row r="170" spans="2:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="170" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B170" s="1"/>
-      <c r="C170" s="1"/>
-    </row>
-    <row r="171" spans="2:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="171" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B171" s="1"/>
-      <c r="C171" s="1"/>
-    </row>
-    <row r="172" spans="2:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="172" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B172" s="1"/>
-      <c r="C172" s="1"/>
-    </row>
-    <row r="173" spans="2:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="173" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B173" s="1"/>
-      <c r="C173" s="1"/>
-    </row>
-    <row r="174" spans="2:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="174" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B174" s="1"/>
-      <c r="C174" s="1"/>
-    </row>
-    <row r="175" spans="2:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="175" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B175" s="1"/>
-      <c r="C175" s="1"/>
-    </row>
-    <row r="176" spans="2:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="176" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B176" s="1"/>
-      <c r="C176" s="1"/>
-    </row>
-    <row r="177" spans="2:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="177" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B177" s="1"/>
-      <c r="C177" s="1"/>
-    </row>
-    <row r="178" spans="2:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="178" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B178" s="1"/>
-      <c r="C178" s="1"/>
-    </row>
-    <row r="179" spans="2:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="179" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B179" s="1"/>
-      <c r="C179" s="1"/>
-    </row>
-    <row r="180" spans="2:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="180" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B180" s="1"/>
-      <c r="C180" s="1"/>
-    </row>
-    <row r="181" spans="2:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="181" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B181" s="1"/>
-      <c r="C181" s="1"/>
-    </row>
-    <row r="182" spans="2:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="182" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B182" s="1"/>
-      <c r="C182" s="1"/>
-    </row>
-    <row r="183" spans="2:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="183" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B183" s="1"/>
-      <c r="C183" s="1"/>
-    </row>
-    <row r="184" spans="2:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="184" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B184" s="1"/>
-      <c r="C184" s="1"/>
-    </row>
-    <row r="185" spans="2:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="185" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B185" s="1"/>
-      <c r="C185" s="1"/>
-    </row>
-    <row r="186" spans="2:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="186" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B186" s="1"/>
-      <c r="C186" s="1"/>
-    </row>
-    <row r="187" spans="2:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="187" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B187" s="1"/>
-      <c r="C187" s="1"/>
-    </row>
-    <row r="188" spans="2:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="188" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B188" s="1"/>
-      <c r="C188" s="1"/>
-    </row>
-    <row r="189" spans="2:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="189" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B189" s="1"/>
-      <c r="C189" s="1"/>
-    </row>
-    <row r="190" spans="2:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="190" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B190" s="1"/>
-      <c r="C190" s="1"/>
-    </row>
-    <row r="191" spans="2:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="191" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B191" s="1"/>
-      <c r="C191" s="1"/>
-    </row>
-    <row r="192" spans="2:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="192" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B192" s="1"/>
-      <c r="C192" s="1"/>
-    </row>
-    <row r="193" spans="2:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="193" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B193" s="1"/>
-      <c r="C193" s="1"/>
-    </row>
-    <row r="194" spans="2:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="194" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B194" s="1"/>
-      <c r="C194" s="1"/>
-    </row>
-    <row r="195" spans="2:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="195" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B195" s="1"/>
-      <c r="C195" s="1"/>
-    </row>
-    <row r="196" spans="2:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="196" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B196" s="1"/>
-      <c r="C196" s="1"/>
-    </row>
-    <row r="197" spans="2:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="197" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B197" s="1"/>
-      <c r="C197" s="1"/>
-    </row>
-    <row r="198" spans="2:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="198" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B198" s="1"/>
-      <c r="C198" s="1"/>
-    </row>
-    <row r="199" spans="2:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="199" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B199" s="1"/>
-      <c r="C199" s="1"/>
-    </row>
-    <row r="200" spans="2:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="200" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B200" s="1"/>
-      <c r="C200" s="1"/>
-    </row>
-    <row r="201" spans="2:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="201" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B201" s="1"/>
-      <c r="C201" s="1"/>
-    </row>
-    <row r="202" spans="2:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="202" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B202" s="1"/>
-      <c r="C202" s="1"/>
-    </row>
-    <row r="203" spans="2:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="203" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B203" s="1"/>
-      <c r="C203" s="1"/>
-    </row>
-    <row r="204" spans="2:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="204" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B204" s="1"/>
-      <c r="C204" s="1"/>
-    </row>
-    <row r="205" spans="2:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="205" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B205" s="1"/>
-      <c r="C205" s="1"/>
-    </row>
-    <row r="206" spans="2:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="206" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B206" s="1"/>
-      <c r="C206" s="1"/>
-    </row>
-    <row r="207" spans="2:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="207" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B207" s="1"/>
-      <c r="C207" s="1"/>
-    </row>
-    <row r="208" spans="2:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="208" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B208" s="1"/>
-      <c r="C208" s="1"/>
-    </row>
-    <row r="209" spans="2:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="209" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B209" s="1"/>
-      <c r="C209" s="1"/>
-    </row>
-    <row r="210" spans="2:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="210" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B210" s="1"/>
-      <c r="C210" s="1"/>
-    </row>
-    <row r="211" spans="2:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="211" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B211" s="1"/>
-      <c r="C211" s="1"/>
-    </row>
-    <row r="212" spans="2:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="212" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B212" s="1"/>
-      <c r="C212" s="1"/>
-    </row>
-    <row r="213" spans="2:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="213" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B213" s="1"/>
-      <c r="C213" s="1"/>
-    </row>
-    <row r="214" spans="2:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="214" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B214" s="1"/>
-      <c r="C214" s="1"/>
-    </row>
-    <row r="215" spans="2:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="215" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B215" s="1"/>
-      <c r="C215" s="1"/>
-    </row>
-    <row r="216" spans="2:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="216" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B216" s="1"/>
-      <c r="C216" s="1"/>
-    </row>
-    <row r="217" spans="2:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="217" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B217" s="1"/>
-      <c r="C217" s="1"/>
-    </row>
-    <row r="218" spans="2:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="218" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B218" s="1"/>
-      <c r="C218" s="1"/>
-    </row>
-    <row r="219" spans="2:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="219" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B219" s="1"/>
-      <c r="C219" s="1"/>
-    </row>
-    <row r="220" spans="2:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="220" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B220" s="1"/>
-      <c r="C220" s="1"/>
-    </row>
-    <row r="221" spans="2:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="221" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B221" s="1"/>
-      <c r="C221" s="1"/>
-    </row>
-    <row r="222" spans="2:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="222" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B222" s="1"/>
-      <c r="C222" s="1"/>
-    </row>
-    <row r="223" spans="2:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="223" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B223" s="1"/>
-      <c r="C223" s="1"/>
-    </row>
-    <row r="224" spans="2:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="224" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B224" s="1"/>
-      <c r="C224" s="1"/>
-    </row>
-    <row r="225" spans="2:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="225" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B225" s="1"/>
-      <c r="C225" s="1"/>
-    </row>
-    <row r="226" spans="2:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="226" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B226" s="1"/>
-      <c r="C226" s="1"/>
-    </row>
-    <row r="227" spans="2:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="227" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B227" s="1"/>
-      <c r="C227" s="1"/>
-    </row>
-    <row r="228" spans="2:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="228" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B228" s="1"/>
-      <c r="C228" s="1"/>
-    </row>
-    <row r="229" spans="2:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="229" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B229" s="1"/>
-      <c r="C229" s="1"/>
-    </row>
-    <row r="230" spans="2:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="230" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B230" s="1"/>
-      <c r="C230" s="1"/>
-    </row>
-    <row r="231" spans="2:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="231" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B231" s="1"/>
-      <c r="C231" s="1"/>
-    </row>
-    <row r="232" spans="2:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="232" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B232" s="1"/>
-      <c r="C232" s="1"/>
-    </row>
-    <row r="233" spans="2:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="233" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B233" s="1"/>
-      <c r="C233" s="1"/>
-    </row>
-    <row r="234" spans="2:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="234" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B234" s="1"/>
-      <c r="C234" s="1"/>
-    </row>
-    <row r="235" spans="2:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="235" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B235" s="1"/>
-      <c r="C235" s="1"/>
-    </row>
-    <row r="236" spans="2:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="236" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B236" s="1"/>
-      <c r="C236" s="1"/>
-    </row>
-    <row r="237" spans="2:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="237" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B237" s="1"/>
-      <c r="C237" s="1"/>
-    </row>
-    <row r="238" spans="2:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="238" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B238" s="1"/>
-      <c r="C238" s="1"/>
-    </row>
-    <row r="239" spans="2:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="239" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B239" s="1"/>
-      <c r="C239" s="1"/>
-    </row>
-    <row r="240" spans="2:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="240" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B240" s="1"/>
-      <c r="C240" s="1"/>
-    </row>
-    <row r="241" spans="2:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="241" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B241" s="1"/>
-      <c r="C241" s="1"/>
-    </row>
-    <row r="242" spans="2:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="242" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B242" s="1"/>
-      <c r="C242" s="1"/>
-    </row>
-    <row r="243" spans="2:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="243" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B243" s="1"/>
-      <c r="C243" s="1"/>
-    </row>
-    <row r="244" spans="2:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="244" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B244" s="1"/>
-      <c r="C244" s="1"/>
-    </row>
-    <row r="245" spans="2:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="245" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B245" s="1"/>
-      <c r="C245" s="1"/>
-    </row>
-    <row r="246" spans="2:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="246" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B246" s="1"/>
-      <c r="C246" s="1"/>
-    </row>
-    <row r="247" spans="2:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="247" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B247" s="1"/>
-      <c r="C247" s="1"/>
-    </row>
-    <row r="248" spans="2:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="248" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B248" s="1"/>
-      <c r="C248" s="1"/>
-    </row>
-    <row r="249" spans="2:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="249" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B249" s="1"/>
-      <c r="C249" s="1"/>
-    </row>
-    <row r="250" spans="2:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="250" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B250" s="1"/>
-      <c r="C250" s="1"/>
-    </row>
-    <row r="251" spans="2:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="251" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B251" s="1"/>
-      <c r="C251" s="1"/>
-    </row>
-    <row r="252" spans="2:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="252" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B252" s="1"/>
-      <c r="C252" s="1"/>
-    </row>
-    <row r="253" spans="2:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="253" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B253" s="1"/>
-      <c r="C253" s="1"/>
-    </row>
-    <row r="254" spans="2:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="254" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B254" s="1"/>
-      <c r="C254" s="1"/>
-    </row>
-    <row r="255" spans="2:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="255" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B255" s="1"/>
-      <c r="C255" s="1"/>
-    </row>
-    <row r="256" spans="2:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="256" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B256" s="1"/>
-      <c r="C256" s="1"/>
-    </row>
-    <row r="257" spans="2:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="257" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B257" s="1"/>
-      <c r="C257" s="1"/>
-    </row>
-    <row r="258" spans="2:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="258" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B258" s="1"/>
-      <c r="C258" s="1"/>
-    </row>
-    <row r="259" spans="2:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="259" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B259" s="1"/>
-      <c r="C259" s="1"/>
-    </row>
-    <row r="260" spans="2:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="260" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B260" s="1"/>
-      <c r="C260" s="1"/>
-    </row>
-    <row r="261" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B261" s="1"/>
-      <c r="C261" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/addresses/good_addresses.xlsx
+++ b/addresses/good_addresses.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="112">
   <si>
     <t>City</t>
   </si>
@@ -241,9 +241,6 @@
   </si>
   <si>
     <t xml:space="preserve">משה רבנו </t>
-  </si>
-  <si>
-    <t xml:space="preserve">יצחק אבינו </t>
   </si>
   <si>
     <t>חתם סופר</t>
@@ -754,7 +751,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H260"/>
+  <dimension ref="A1:H256"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.8984375" bestFit="1" customWidth="1"/>
@@ -775,7 +772,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E1" s="2"/>
     </row>
@@ -1050,7 +1047,7 @@
         <v>3</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>15</v>
@@ -1067,7 +1064,7 @@
         <v>14</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D22" s="8">
         <v>45966</v>
@@ -1078,10 +1075,10 @@
         <v>3</v>
       </c>
       <c r="B23" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C23" s="1" t="s">
         <v>77</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>78</v>
       </c>
       <c r="D23" s="8">
         <v>45966</v>
@@ -1092,7 +1089,7 @@
         <v>3</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>9</v>
@@ -1106,10 +1103,10 @@
         <v>3</v>
       </c>
       <c r="B25" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C25" s="1" t="s">
         <v>80</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>81</v>
       </c>
       <c r="D25" s="8">
         <v>45966</v>
@@ -1120,7 +1117,7 @@
         <v>3</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>9</v>
@@ -1137,7 +1134,7 @@
         <v>24</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D27" s="8">
         <v>45966</v>
@@ -1148,10 +1145,10 @@
         <v>3</v>
       </c>
       <c r="B28" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C28" s="1" t="s">
         <v>83</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>84</v>
       </c>
       <c r="D28" s="8">
         <v>45966</v>
@@ -1162,10 +1159,10 @@
         <v>3</v>
       </c>
       <c r="B29" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C29" s="1" t="s">
         <v>85</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>86</v>
       </c>
       <c r="D29" s="8">
         <v>45966</v>
@@ -1190,10 +1187,10 @@
         <v>3</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D31" s="8">
         <v>45966</v>
@@ -1204,10 +1201,10 @@
         <v>3</v>
       </c>
       <c r="B32" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C32" s="1" t="s">
         <v>88</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>89</v>
       </c>
       <c r="D32" s="8">
         <v>45966</v>
@@ -1218,10 +1215,10 @@
         <v>3</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D33" s="8">
         <v>45966</v>
@@ -1246,7 +1243,7 @@
         <v>3</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>21</v>
@@ -1260,7 +1257,7 @@
         <v>3</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>26</v>
@@ -1274,10 +1271,10 @@
         <v>3</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D37" s="8">
         <v>45966</v>
@@ -1291,10 +1288,10 @@
         <v>3</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D38" s="8">
         <v>45966</v>
@@ -1308,7 +1305,7 @@
         <v>3</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>28</v>
@@ -1324,10 +1321,10 @@
         <v>3</v>
       </c>
       <c r="B40" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C40" s="1" t="s">
         <v>96</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>97</v>
       </c>
       <c r="D40" s="8">
         <v>45966</v>
@@ -1340,7 +1337,7 @@
         <v>3</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>19</v>
@@ -1354,7 +1351,7 @@
         <v>3</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>27</v>
@@ -1368,7 +1365,7 @@
         <v>3</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>15</v>
@@ -1382,7 +1379,7 @@
         <v>3</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>13</v>
@@ -1396,10 +1393,10 @@
         <v>3</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D45" s="8">
         <v>45966</v>
@@ -1410,7 +1407,7 @@
         <v>3</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>26</v>
@@ -1427,7 +1424,7 @@
         <v>6</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D47" s="8">
         <v>45966</v>
@@ -1438,7 +1435,7 @@
         <v>3</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>27</v>
@@ -1452,7 +1449,7 @@
         <v>3</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>16</v>
@@ -1497,7 +1494,7 @@
         <v>6</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D52" s="8">
         <v>45966</v>
@@ -1508,7 +1505,7 @@
         <v>3</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>28</v>
@@ -1525,7 +1522,7 @@
         <v>14</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D54" s="8">
         <v>45966</v>
@@ -1536,10 +1533,10 @@
         <v>3</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D55" s="8">
         <v>45966</v>
@@ -1550,10 +1547,10 @@
         <v>3</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D56" s="8">
         <v>45966</v>
@@ -1567,7 +1564,7 @@
         <v>24</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D57" s="8">
         <v>45966</v>
@@ -1578,10 +1575,10 @@
         <v>3</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D58" s="8">
         <v>45966</v>
@@ -1595,7 +1592,7 @@
         <v>14</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D59" s="8">
         <v>45966</v>
@@ -1606,10 +1603,10 @@
         <v>3</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D60" s="8">
         <v>45966</v>
@@ -1620,10 +1617,10 @@
         <v>3</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D61" s="8">
         <v>45966</v>
@@ -1634,10 +1631,10 @@
         <v>3</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D62" s="8">
         <v>45966</v>
@@ -1651,7 +1648,7 @@
         <v>24</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D63" s="8">
         <v>45966</v>
@@ -1676,7 +1673,7 @@
         <v>3</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>15</v>
@@ -1693,7 +1690,7 @@
         <v>14</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D66" s="8">
         <v>45966</v>
@@ -1704,7 +1701,7 @@
         <v>3</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>21</v>
@@ -1721,7 +1718,7 @@
         <v>14</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D68" s="8">
         <v>45966</v>
@@ -1732,7 +1729,7 @@
         <v>3</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>15</v>
@@ -2736,46 +2733,13 @@
       </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A141" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B141" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="C141" s="6">
-        <v>8</v>
-      </c>
-      <c r="D141" s="8">
-        <v>45694</v>
-      </c>
+      <c r="B141" s="1"/>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A142" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B142" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C142" s="6">
-        <v>7</v>
-      </c>
-      <c r="D142" s="8">
-        <v>45694</v>
-      </c>
+      <c r="B142" s="1"/>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A143" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B143" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C143" s="6">
-        <v>17</v>
-      </c>
-      <c r="D143" s="8">
-        <v>45694</v>
-      </c>
+      <c r="B143" s="1"/>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B144" s="1"/>
@@ -3115,18 +3079,6 @@
     </row>
     <row r="256" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B256" s="1"/>
-    </row>
-    <row r="257" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B257" s="1"/>
-    </row>
-    <row r="258" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B258" s="1"/>
-    </row>
-    <row r="259" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B259" s="1"/>
-    </row>
-    <row r="260" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B260" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/addresses/good_addresses.xlsx
+++ b/addresses/good_addresses.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="113">
   <si>
     <t>City</t>
   </si>
@@ -355,6 +355,9 @@
   </si>
   <si>
     <t>required_delivery_date</t>
+  </si>
+  <si>
+    <t>14/5/2026</t>
   </si>
 </sst>
 </file>
@@ -378,7 +381,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -394,6 +397,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="3" tint="0.749992370372631"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -425,7 +440,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -449,6 +464,20 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -777,214 +806,229 @@
       <c r="E1" s="2"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="1" t="s">
+      <c r="A2" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="8">
-        <v>45966</v>
-      </c>
+      <c r="D2" s="9">
+        <v>46331</v>
+      </c>
+      <c r="E2" s="14"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="1" t="s">
+      <c r="A3" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="8">
-        <v>45966</v>
-      </c>
+      <c r="D3" s="9">
+        <v>46331</v>
+      </c>
+      <c r="E3" s="14"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="1" t="s">
+      <c r="A4" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="8">
-        <v>45966</v>
-      </c>
+      <c r="D4" s="9">
+        <v>46331</v>
+      </c>
+      <c r="E4" s="14"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="1" t="s">
+      <c r="A5" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="8">
-        <v>45966</v>
-      </c>
+      <c r="D5" s="9">
+        <v>46331</v>
+      </c>
+      <c r="E5" s="14"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="1" t="s">
+      <c r="A6" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="8">
-        <v>45966</v>
-      </c>
+      <c r="D6" s="9">
+        <v>46331</v>
+      </c>
+      <c r="E6" s="14"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" s="1" t="s">
+      <c r="A7" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="8">
-        <v>45966</v>
-      </c>
+      <c r="D7" s="9">
+        <v>46331</v>
+      </c>
+      <c r="E7" s="14"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" s="1" t="s">
+      <c r="A8" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="D8" s="8">
-        <v>45966</v>
-      </c>
+      <c r="D8" s="9">
+        <v>46331</v>
+      </c>
+      <c r="E8" s="14"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" s="1" t="s">
+      <c r="A9" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="D9" s="8">
-        <v>45966</v>
-      </c>
+      <c r="D9" s="9">
+        <v>46331</v>
+      </c>
+      <c r="E9" s="14"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10" s="1" t="s">
+      <c r="A10" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="D10" s="8">
-        <v>45966</v>
-      </c>
+      <c r="D10" s="9">
+        <v>46331</v>
+      </c>
+      <c r="E10" s="14"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B11" s="1" t="s">
+      <c r="A11" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C11" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="D11" s="8">
-        <v>45966</v>
-      </c>
+      <c r="D11" s="9">
+        <v>46331</v>
+      </c>
+      <c r="E11" s="14"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>3</v>
-      </c>
-      <c r="B12" s="1" t="s">
+      <c r="A12" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C12" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="D12" s="8">
-        <v>45966</v>
-      </c>
+      <c r="D12" s="9">
+        <v>46331</v>
+      </c>
+      <c r="E12" s="14"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>3</v>
-      </c>
-      <c r="B13" s="1" t="s">
+      <c r="A13" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B13" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="C13" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="D13" s="8">
-        <v>45966</v>
-      </c>
+      <c r="D13" s="9">
+        <v>46331</v>
+      </c>
+      <c r="E13" s="14"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>3</v>
-      </c>
-      <c r="B14" s="1" t="s">
+      <c r="A14" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B14" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C14" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="D14" s="8">
-        <v>45966</v>
-      </c>
+      <c r="D14" s="9">
+        <v>46331</v>
+      </c>
+      <c r="E14" s="14"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>3</v>
-      </c>
-      <c r="B15" s="1" t="s">
+      <c r="A15" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B15" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="C15" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="D15" s="8">
-        <v>45966</v>
-      </c>
+      <c r="D15" s="9">
+        <v>46331</v>
+      </c>
+      <c r="E15" s="14"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>3</v>
-      </c>
-      <c r="B16" s="1" t="s">
+      <c r="A16" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B16" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="C16" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="D16" s="8">
-        <v>45966</v>
-      </c>
+      <c r="D16" s="9">
+        <v>46331</v>
+      </c>
+      <c r="E16" s="14"/>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
@@ -997,7 +1041,7 @@
         <v>18</v>
       </c>
       <c r="D17" s="8">
-        <v>45966</v>
+        <v>46361</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -1011,7 +1055,7 @@
         <v>28</v>
       </c>
       <c r="D18" s="8">
-        <v>45966</v>
+        <v>46361</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1025,7 +1069,7 @@
         <v>25</v>
       </c>
       <c r="D19" s="8">
-        <v>45966</v>
+        <v>46361</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1039,7 +1083,7 @@
         <v>29</v>
       </c>
       <c r="D20" s="8">
-        <v>45966</v>
+        <v>46361</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -1053,7 +1097,7 @@
         <v>15</v>
       </c>
       <c r="D21" s="8">
-        <v>45966</v>
+        <v>46361</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -1067,7 +1111,7 @@
         <v>75</v>
       </c>
       <c r="D22" s="8">
-        <v>45966</v>
+        <v>46361</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -1081,7 +1125,7 @@
         <v>77</v>
       </c>
       <c r="D23" s="8">
-        <v>45966</v>
+        <v>46361</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -1095,7 +1139,7 @@
         <v>9</v>
       </c>
       <c r="D24" s="8">
-        <v>45966</v>
+        <v>46361</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1109,7 +1153,7 @@
         <v>80</v>
       </c>
       <c r="D25" s="8">
-        <v>45966</v>
+        <v>46361</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -1123,7 +1167,7 @@
         <v>9</v>
       </c>
       <c r="D26" s="8">
-        <v>45966</v>
+        <v>46361</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -1137,7 +1181,7 @@
         <v>81</v>
       </c>
       <c r="D27" s="8">
-        <v>45966</v>
+        <v>46361</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -1151,7 +1195,7 @@
         <v>83</v>
       </c>
       <c r="D28" s="8">
-        <v>45966</v>
+        <v>46361</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -1165,7 +1209,7 @@
         <v>85</v>
       </c>
       <c r="D29" s="8">
-        <v>45966</v>
+        <v>46361</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1179,7 +1223,7 @@
         <v>27</v>
       </c>
       <c r="D30" s="8">
-        <v>45966</v>
+        <v>46361</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -1193,7 +1237,7 @@
         <v>86</v>
       </c>
       <c r="D31" s="8">
-        <v>45966</v>
+        <v>46300</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -1207,7 +1251,7 @@
         <v>88</v>
       </c>
       <c r="D32" s="8">
-        <v>45966</v>
+        <v>46300</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
@@ -1221,7 +1265,7 @@
         <v>89</v>
       </c>
       <c r="D33" s="8">
-        <v>45966</v>
+        <v>46300</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
@@ -1235,7 +1279,7 @@
         <v>5</v>
       </c>
       <c r="D34" s="8">
-        <v>45966</v>
+        <v>46300</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
@@ -1249,7 +1293,7 @@
         <v>21</v>
       </c>
       <c r="D35" s="8">
-        <v>45966</v>
+        <v>46332</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
@@ -1263,7 +1307,7 @@
         <v>26</v>
       </c>
       <c r="D36" s="8">
-        <v>45966</v>
+        <v>46332</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
@@ -1277,7 +1321,7 @@
         <v>92</v>
       </c>
       <c r="D37" s="8">
-        <v>45966</v>
+        <v>46332</v>
       </c>
       <c r="F37" s="3"/>
       <c r="G37" s="4"/>
@@ -1294,7 +1338,7 @@
         <v>93</v>
       </c>
       <c r="D38" s="8">
-        <v>45966</v>
+        <v>46332</v>
       </c>
       <c r="F38" s="3"/>
       <c r="G38" s="4"/>
@@ -1311,7 +1355,7 @@
         <v>28</v>
       </c>
       <c r="D39" s="8">
-        <v>45966</v>
+        <v>46332</v>
       </c>
       <c r="G39" s="1"/>
       <c r="H39" s="1"/>
@@ -1327,7 +1371,7 @@
         <v>96</v>
       </c>
       <c r="D40" s="8">
-        <v>45966</v>
+        <v>46332</v>
       </c>
       <c r="G40" s="1"/>
       <c r="H40" s="1"/>
@@ -1343,7 +1387,7 @@
         <v>19</v>
       </c>
       <c r="D41" s="8">
-        <v>45966</v>
+        <v>46332</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
@@ -1357,7 +1401,7 @@
         <v>27</v>
       </c>
       <c r="D42" s="8">
-        <v>45966</v>
+        <v>46332</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
@@ -1371,7 +1415,7 @@
         <v>15</v>
       </c>
       <c r="D43" s="8">
-        <v>45966</v>
+        <v>46332</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
@@ -1385,7 +1429,7 @@
         <v>13</v>
       </c>
       <c r="D44" s="8">
-        <v>45966</v>
+        <v>46332</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
@@ -1399,7 +1443,7 @@
         <v>81</v>
       </c>
       <c r="D45" s="8">
-        <v>45966</v>
+        <v>46332</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
@@ -1413,7 +1457,7 @@
         <v>26</v>
       </c>
       <c r="D46" s="8">
-        <v>45966</v>
+        <v>46332</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
@@ -1427,7 +1471,7 @@
         <v>75</v>
       </c>
       <c r="D47" s="8">
-        <v>45966</v>
+        <v>46332</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
@@ -1441,7 +1485,7 @@
         <v>27</v>
       </c>
       <c r="D48" s="8">
-        <v>45966</v>
+        <v>46332</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
@@ -1455,7 +1499,7 @@
         <v>16</v>
       </c>
       <c r="D49" s="8">
-        <v>45966</v>
+        <v>46332</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -1469,7 +1513,7 @@
         <v>28</v>
       </c>
       <c r="D50" s="8">
-        <v>45966</v>
+        <v>46332</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
@@ -1483,7 +1527,7 @@
         <v>28</v>
       </c>
       <c r="D51" s="8">
-        <v>45966</v>
+        <v>46332</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
@@ -1497,7 +1541,7 @@
         <v>99</v>
       </c>
       <c r="D52" s="8">
-        <v>45966</v>
+        <v>46332</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
@@ -1511,7 +1555,7 @@
         <v>28</v>
       </c>
       <c r="D53" s="8">
-        <v>45966</v>
+        <v>46332</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
@@ -1525,7 +1569,7 @@
         <v>101</v>
       </c>
       <c r="D54" s="8">
-        <v>45966</v>
+        <v>46332</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
@@ -1539,7 +1583,7 @@
         <v>102</v>
       </c>
       <c r="D55" s="8">
-        <v>45966</v>
+        <v>46332</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
@@ -1553,7 +1597,7 @@
         <v>103</v>
       </c>
       <c r="D56" s="8">
-        <v>45966</v>
+        <v>46332</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
@@ -1567,7 +1611,7 @@
         <v>104</v>
       </c>
       <c r="D57" s="8">
-        <v>45966</v>
+        <v>46300</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
@@ -1581,7 +1625,7 @@
         <v>105</v>
       </c>
       <c r="D58" s="8">
-        <v>45966</v>
+        <v>46300</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
@@ -1595,7 +1639,7 @@
         <v>106</v>
       </c>
       <c r="D59" s="8">
-        <v>45966</v>
+        <v>46300</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
@@ -1609,7 +1653,7 @@
         <v>107</v>
       </c>
       <c r="D60" s="8">
-        <v>45966</v>
+        <v>46300</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
@@ -1623,7 +1667,7 @@
         <v>86</v>
       </c>
       <c r="D61" s="8">
-        <v>45966</v>
+        <v>46300</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
@@ -1637,7 +1681,7 @@
         <v>101</v>
       </c>
       <c r="D62" s="8">
-        <v>45966</v>
+        <v>46300</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
@@ -1651,7 +1695,7 @@
         <v>108</v>
       </c>
       <c r="D63" s="8">
-        <v>45966</v>
+        <v>46300</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
@@ -1665,10 +1709,10 @@
         <v>9</v>
       </c>
       <c r="D64" s="8">
-        <v>45966</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46300</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>3</v>
       </c>
@@ -1678,11 +1722,11 @@
       <c r="C65" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D65" s="8">
-        <v>45966</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D65" s="8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>3</v>
       </c>
@@ -1692,11 +1736,11 @@
       <c r="C66" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="D66" s="8">
-        <v>45966</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D66" s="8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>3</v>
       </c>
@@ -1706,11 +1750,11 @@
       <c r="C67" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D67" s="8">
-        <v>45966</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D67" s="8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>3</v>
       </c>
@@ -1720,11 +1764,11 @@
       <c r="C68" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="D68" s="8">
-        <v>45966</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D68" s="8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>3</v>
       </c>
@@ -1734,288 +1778,293 @@
       <c r="C69" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D69" s="8">
-        <v>45966</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
-        <v>40</v>
-      </c>
-      <c r="B70" s="1" t="s">
+      <c r="D69" s="8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A70" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="B70" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="C70" s="1">
+      <c r="C70" s="11">
         <v>38</v>
       </c>
-      <c r="D70" s="8">
-        <v>45966</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
-        <v>40</v>
-      </c>
-      <c r="B71" s="1" t="s">
+      <c r="D70" s="9">
+        <v>46331</v>
+      </c>
+      <c r="E70" s="14"/>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A71" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="B71" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="C71" s="1">
+      <c r="C71" s="11">
         <v>38</v>
       </c>
-      <c r="D71" s="8">
-        <v>45966</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
-        <v>40</v>
-      </c>
-      <c r="B72" s="1" t="s">
+      <c r="D71" s="9">
+        <v>46331</v>
+      </c>
+      <c r="E71" s="14"/>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A72" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="B72" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="C72" s="1">
+      <c r="C72" s="11">
         <v>47</v>
       </c>
-      <c r="D72" s="8">
-        <v>45966</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
-        <v>40</v>
-      </c>
-      <c r="B73" s="1" t="s">
+      <c r="D72" s="9">
+        <v>46331</v>
+      </c>
+      <c r="E72" s="14"/>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A73" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="B73" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="C73" s="1">
+      <c r="C73" s="11">
         <v>37</v>
       </c>
-      <c r="D73" s="8">
-        <v>45966</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
-        <v>40</v>
-      </c>
-      <c r="B74" s="1" t="s">
+      <c r="D73" s="9">
+        <v>46331</v>
+      </c>
+      <c r="E73" s="14"/>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A74" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="B74" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="C74" s="1">
+      <c r="C74" s="11">
         <v>37</v>
       </c>
-      <c r="D74" s="8">
-        <v>45966</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
-        <v>40</v>
-      </c>
-      <c r="B75" s="1" t="s">
+      <c r="D74" s="9">
+        <v>46331</v>
+      </c>
+      <c r="E74" s="14"/>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A75" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="B75" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="C75" s="1">
+      <c r="C75" s="11">
         <v>17</v>
       </c>
-      <c r="D75" s="8">
-        <v>45966</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
-        <v>40</v>
-      </c>
-      <c r="B76" s="1" t="s">
+      <c r="D75" s="9">
+        <v>46331</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A76" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="B76" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="C76" s="1">
+      <c r="C76" s="11">
         <v>1</v>
       </c>
-      <c r="D76" s="8">
-        <v>45966</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
-        <v>40</v>
-      </c>
-      <c r="B77" s="1" t="s">
+      <c r="D76" s="9">
+        <v>46331</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A77" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="B77" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="C77" s="1">
+      <c r="C77" s="11">
         <v>4</v>
       </c>
-      <c r="D77" s="8">
-        <v>45966</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
-        <v>40</v>
-      </c>
-      <c r="B78" s="1" t="s">
+      <c r="D77" s="9">
+        <v>46331</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A78" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="B78" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="C78" s="1">
+      <c r="C78" s="11">
         <v>5</v>
       </c>
-      <c r="D78" s="8">
-        <v>45966</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A79" t="s">
-        <v>40</v>
-      </c>
-      <c r="B79" s="1" t="s">
+      <c r="D78" s="9">
+        <v>46331</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A79" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="B79" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="C79" s="1">
+      <c r="C79" s="11">
         <v>28</v>
       </c>
-      <c r="D79" s="8">
-        <v>45966</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A80" t="s">
-        <v>40</v>
-      </c>
-      <c r="B80" s="1" t="s">
+      <c r="D79" s="9">
+        <v>46331</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A80" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="B80" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="C80" s="1">
+      <c r="C80" s="11">
         <v>24</v>
       </c>
-      <c r="D80" s="8">
-        <v>45966</v>
+      <c r="D80" s="9">
+        <v>46331</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
-        <v>40</v>
-      </c>
-      <c r="B81" s="1" t="s">
+      <c r="A81" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="B81" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="C81" s="1">
+      <c r="C81" s="11">
         <v>38</v>
       </c>
-      <c r="D81" s="8">
-        <v>45966</v>
+      <c r="D81" s="9">
+        <v>46331</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
-        <v>40</v>
-      </c>
-      <c r="B82" s="1" t="s">
+      <c r="A82" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="B82" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C82" s="1">
+      <c r="C82" s="11">
         <v>36</v>
       </c>
-      <c r="D82" s="8">
-        <v>45966</v>
+      <c r="D82" s="9">
+        <v>46331</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A83" t="s">
-        <v>40</v>
-      </c>
-      <c r="B83" s="1" t="s">
+      <c r="A83" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="B83" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="C83" s="1">
+      <c r="C83" s="11">
         <v>32</v>
       </c>
-      <c r="D83" s="8">
-        <v>45966</v>
+      <c r="D83" s="9">
+        <v>46331</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A84" t="s">
-        <v>40</v>
-      </c>
-      <c r="B84" s="1" t="s">
+      <c r="A84" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="B84" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="C84" s="1">
+      <c r="C84" s="11">
         <v>13</v>
       </c>
-      <c r="D84" s="8">
-        <v>45966</v>
+      <c r="D84" s="9">
+        <v>46331</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A85" t="s">
-        <v>40</v>
-      </c>
-      <c r="B85" s="1" t="s">
+      <c r="A85" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="B85" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="C85" s="1">
+      <c r="C85" s="11">
         <v>13</v>
       </c>
-      <c r="D85" s="8">
-        <v>45966</v>
+      <c r="D85" s="9">
+        <v>46331</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A86" t="s">
-        <v>40</v>
-      </c>
-      <c r="B86" s="1" t="s">
+      <c r="A86" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="B86" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="C86" s="1">
-        <v>30</v>
-      </c>
-      <c r="D86" s="8">
-        <v>45966</v>
+      <c r="C86" s="11">
+        <v>30</v>
+      </c>
+      <c r="D86" s="9">
+        <v>46331</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A87" t="s">
-        <v>40</v>
-      </c>
-      <c r="B87" s="1" t="s">
+      <c r="A87" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="B87" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="C87" s="1">
+      <c r="C87" s="11">
         <v>4</v>
       </c>
-      <c r="D87" s="8">
-        <v>45966</v>
+      <c r="D87" s="9">
+        <v>46331</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A88" t="s">
-        <v>40</v>
-      </c>
-      <c r="B88" s="1" t="s">
+      <c r="A88" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="B88" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="C88" s="1">
+      <c r="C88" s="11">
         <v>6</v>
       </c>
-      <c r="D88" s="8">
-        <v>45966</v>
+      <c r="D88" s="9">
+        <v>46331</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A89" t="s">
-        <v>40</v>
-      </c>
-      <c r="B89" s="1" t="s">
+      <c r="A89" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="B89" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="C89" s="1">
+      <c r="C89" s="11">
         <v>5</v>
       </c>
-      <c r="D89" s="8">
-        <v>45966</v>
+      <c r="D89" s="9">
+        <v>46331</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
@@ -2029,7 +2078,7 @@
         <v>2</v>
       </c>
       <c r="D90" s="8">
-        <v>45966</v>
+        <v>46361</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
@@ -2043,7 +2092,7 @@
         <v>13</v>
       </c>
       <c r="D91" s="8">
-        <v>45966</v>
+        <v>46361</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
@@ -2057,7 +2106,7 @@
         <v>14</v>
       </c>
       <c r="D92" s="8">
-        <v>45966</v>
+        <v>46361</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
@@ -2071,7 +2120,7 @@
         <v>40</v>
       </c>
       <c r="D93" s="8">
-        <v>45966</v>
+        <v>46361</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
@@ -2085,7 +2134,7 @@
         <v>50</v>
       </c>
       <c r="D94" s="8">
-        <v>45966</v>
+        <v>46361</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
@@ -2099,7 +2148,7 @@
         <v>59</v>
       </c>
       <c r="D95" s="8">
-        <v>45966</v>
+        <v>46361</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
@@ -2113,10 +2162,10 @@
         <v>13</v>
       </c>
       <c r="D96" s="8">
-        <v>45966</v>
-      </c>
-    </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46361</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>40</v>
       </c>
@@ -2127,10 +2176,10 @@
         <v>8</v>
       </c>
       <c r="D97" s="8">
-        <v>45966</v>
-      </c>
-    </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46361</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>40</v>
       </c>
@@ -2141,10 +2190,10 @@
         <v>15</v>
       </c>
       <c r="D98" s="8">
-        <v>45966</v>
-      </c>
-    </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46361</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>40</v>
       </c>
@@ -2155,10 +2204,10 @@
         <v>16</v>
       </c>
       <c r="D99" s="8">
-        <v>45966</v>
-      </c>
-    </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46361</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>40</v>
       </c>
@@ -2169,10 +2218,10 @@
         <v>26</v>
       </c>
       <c r="D100" s="8">
-        <v>45966</v>
-      </c>
-    </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46361</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>40</v>
       </c>
@@ -2183,10 +2232,10 @@
         <v>20</v>
       </c>
       <c r="D101" s="8">
-        <v>45966</v>
-      </c>
-    </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46361</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>40</v>
       </c>
@@ -2197,10 +2246,10 @@
         <v>31</v>
       </c>
       <c r="D102" s="8">
-        <v>45966</v>
-      </c>
-    </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46361</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>40</v>
       </c>
@@ -2211,10 +2260,10 @@
         <v>14</v>
       </c>
       <c r="D103" s="8">
-        <v>45966</v>
-      </c>
-    </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46361</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>40</v>
       </c>
@@ -2225,10 +2274,10 @@
         <v>12</v>
       </c>
       <c r="D104" s="8">
-        <v>45966</v>
-      </c>
-    </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46361</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" s="4" t="s">
         <v>30</v>
       </c>
@@ -2239,10 +2288,10 @@
         <v>46</v>
       </c>
       <c r="D105" s="8">
-        <v>45966</v>
-      </c>
-    </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46361</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
         <v>30</v>
       </c>
@@ -2253,10 +2302,10 @@
         <v>6</v>
       </c>
       <c r="D106" s="8">
-        <v>45966</v>
-      </c>
-    </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46361</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" s="4" t="s">
         <v>30</v>
       </c>
@@ -2267,10 +2316,10 @@
         <v>3</v>
       </c>
       <c r="D107" s="8">
-        <v>45966</v>
-      </c>
-    </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46361</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
         <v>30</v>
       </c>
@@ -2281,10 +2330,10 @@
         <v>8</v>
       </c>
       <c r="D108" s="8">
-        <v>45966</v>
-      </c>
-    </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46361</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" s="4" t="s">
         <v>30</v>
       </c>
@@ -2295,10 +2344,10 @@
         <v>5</v>
       </c>
       <c r="D109" s="8">
-        <v>45966</v>
-      </c>
-    </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46361</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
         <v>30</v>
       </c>
@@ -2309,10 +2358,10 @@
         <v>7</v>
       </c>
       <c r="D110" s="8">
-        <v>45966</v>
-      </c>
-    </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46361</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" s="4" t="s">
         <v>30</v>
       </c>
@@ -2323,290 +2372,310 @@
         <v>7</v>
       </c>
       <c r="D111" s="8">
-        <v>45966</v>
-      </c>
-    </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A112" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B112" s="5" t="s">
+        <v>46361</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A112" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="B112" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="C112" s="4">
+      <c r="C112" s="12">
         <v>7</v>
       </c>
-      <c r="D112" s="8">
-        <v>45966</v>
-      </c>
-    </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A113" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B113" s="5" t="s">
+      <c r="D112" s="9">
+        <v>46331</v>
+      </c>
+      <c r="E112" s="14"/>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A113" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="B113" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="C113" s="4">
+      <c r="C113" s="12">
         <v>12</v>
       </c>
-      <c r="D113" s="8">
-        <v>45996</v>
-      </c>
-    </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A114" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B114" s="5" t="s">
+      <c r="D113" s="9">
+        <v>46331</v>
+      </c>
+      <c r="E113" s="14"/>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A114" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="B114" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="C114" s="4">
+      <c r="C114" s="12">
         <v>7</v>
       </c>
-      <c r="D114" s="8">
-        <v>45996</v>
-      </c>
-    </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A115" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B115" s="5" t="s">
+      <c r="D114" s="9">
+        <v>46331</v>
+      </c>
+      <c r="E114" s="14"/>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A115" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="B115" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C115" s="4">
-        <v>3</v>
-      </c>
-      <c r="D115" s="8">
-        <v>45996</v>
-      </c>
-    </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A116" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B116" s="5" t="s">
+      <c r="C115" s="12">
+        <v>3</v>
+      </c>
+      <c r="D115" s="9">
+        <v>46331</v>
+      </c>
+      <c r="E115" s="14"/>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A116" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="B116" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="C116" s="4">
+      <c r="C116" s="12">
         <v>5</v>
       </c>
-      <c r="D116" s="8">
-        <v>45996</v>
-      </c>
-    </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A117" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B117" s="5" t="s">
+      <c r="D116" s="9">
+        <v>46331</v>
+      </c>
+      <c r="E116" s="14"/>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A117" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="B117" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C117" s="4">
+      <c r="C117" s="12">
         <v>43</v>
       </c>
-      <c r="D117" s="8">
-        <v>45996</v>
-      </c>
-    </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A118" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B118" s="5" t="s">
+      <c r="D117" s="9">
+        <v>46331</v>
+      </c>
+      <c r="E117" s="14"/>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A118" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="B118" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C118" s="4">
+      <c r="C118" s="12">
         <v>8</v>
       </c>
-      <c r="D118" s="8">
-        <v>45996</v>
-      </c>
-    </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A119" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B119" s="5" t="s">
+      <c r="D118" s="9">
+        <v>46331</v>
+      </c>
+      <c r="E118" s="14"/>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A119" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="B119" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="C119" s="4">
+      <c r="C119" s="12">
         <v>15</v>
       </c>
-      <c r="D119" s="8">
-        <v>45996</v>
-      </c>
-    </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A120" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B120" s="5" t="s">
+      <c r="D119" s="9">
+        <v>46331</v>
+      </c>
+      <c r="E119" s="14"/>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A120" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="B120" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="C120" s="4">
+      <c r="C120" s="12">
         <v>11</v>
       </c>
-      <c r="D120" s="8">
-        <v>45996</v>
-      </c>
-    </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A121" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B121" s="1" t="s">
+      <c r="D120" s="9">
+        <v>46331</v>
+      </c>
+      <c r="E120" s="14"/>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A121" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="B121" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="C121" s="6">
+      <c r="C121" s="12">
         <v>12</v>
       </c>
-      <c r="D121" s="8">
-        <v>45996</v>
-      </c>
-    </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A122" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B122" s="1" t="s">
+      <c r="D121" s="9">
+        <v>46331</v>
+      </c>
+      <c r="E121" s="14"/>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A122" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="B122" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="C122" s="6">
+      <c r="C122" s="12">
         <v>9</v>
       </c>
-      <c r="D122" s="8">
-        <v>45996</v>
-      </c>
-    </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A123" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B123" s="1" t="s">
+      <c r="D122" s="9">
+        <v>46331</v>
+      </c>
+      <c r="E122" s="14"/>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A123" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="B123" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="C123" s="6">
-        <v>30</v>
-      </c>
-      <c r="D123" s="8">
-        <v>45996</v>
-      </c>
-    </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A124" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B124" s="1" t="s">
+      <c r="C123" s="12">
+        <v>30</v>
+      </c>
+      <c r="D123" s="9">
+        <v>46331</v>
+      </c>
+      <c r="E123" s="14"/>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A124" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="B124" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="C124" s="6">
+      <c r="C124" s="12">
         <v>9</v>
       </c>
-      <c r="D124" s="8">
-        <v>45996</v>
-      </c>
-    </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A125" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B125" s="1" t="s">
+      <c r="D124" s="9">
+        <v>46331</v>
+      </c>
+      <c r="E124" s="14"/>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A125" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="B125" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="C125" s="6">
+      <c r="C125" s="12">
         <v>16</v>
       </c>
-      <c r="D125" s="8">
-        <v>45996</v>
-      </c>
-    </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A126" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B126" s="1" t="s">
+      <c r="D125" s="9">
+        <v>46331</v>
+      </c>
+      <c r="E125" s="14"/>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A126" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="B126" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="C126" s="6">
+      <c r="C126" s="12">
         <v>1</v>
       </c>
-      <c r="D126" s="8">
-        <v>45996</v>
-      </c>
-    </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A127" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B127" s="1" t="s">
+      <c r="D126" s="9">
+        <v>46331</v>
+      </c>
+      <c r="E126" s="14"/>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A127" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="B127" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="C127" s="6">
+      <c r="C127" s="12">
         <v>21</v>
       </c>
-      <c r="D127" s="8">
-        <v>45996</v>
-      </c>
-    </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A128" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B128" s="1" t="s">
+      <c r="D127" s="9">
+        <v>46331</v>
+      </c>
+      <c r="E127" s="14"/>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A128" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="B128" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="C128" s="6">
+      <c r="C128" s="12">
         <v>32</v>
       </c>
-      <c r="D128" s="8">
-        <v>45694</v>
-      </c>
-    </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A129" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B129" s="1" t="s">
+      <c r="D128" s="9">
+        <v>46331</v>
+      </c>
+      <c r="E128" s="14"/>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A129" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="B129" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="C129" s="6">
+      <c r="C129" s="12">
         <v>25</v>
       </c>
-      <c r="D129" s="8">
-        <v>45694</v>
-      </c>
-    </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A130" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B130" s="1" t="s">
+      <c r="D129" s="9">
+        <v>46331</v>
+      </c>
+      <c r="E129" s="14"/>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A130" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="B130" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="C130" s="6">
+      <c r="C130" s="12">
         <v>20</v>
       </c>
-      <c r="D130" s="8">
-        <v>45694</v>
-      </c>
-    </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A131" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B131" s="1" t="s">
+      <c r="D130" s="9">
+        <v>46331</v>
+      </c>
+      <c r="E130" s="14"/>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A131" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="B131" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="C131" s="6">
-        <v>3</v>
-      </c>
-      <c r="D131" s="8">
-        <v>45694</v>
-      </c>
-    </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C131" s="12">
+        <v>3</v>
+      </c>
+      <c r="D131" s="9">
+        <v>46331</v>
+      </c>
+      <c r="E131" s="14"/>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
         <v>30</v>
       </c>
@@ -2617,10 +2686,10 @@
         <v>21</v>
       </c>
       <c r="D132" s="8">
-        <v>45694</v>
-      </c>
-    </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46059</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A133" s="4" t="s">
         <v>30</v>
       </c>
@@ -2631,10 +2700,10 @@
         <v>19</v>
       </c>
       <c r="D133" s="8">
-        <v>45694</v>
-      </c>
-    </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46059</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
         <v>30</v>
       </c>
@@ -2645,10 +2714,10 @@
         <v>5</v>
       </c>
       <c r="D134" s="8">
-        <v>45694</v>
-      </c>
-    </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46059</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A135" s="4" t="s">
         <v>30</v>
       </c>
@@ -2659,10 +2728,10 @@
         <v>7</v>
       </c>
       <c r="D135" s="8">
-        <v>45694</v>
-      </c>
-    </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46059</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
         <v>30</v>
       </c>
@@ -2673,10 +2742,10 @@
         <v>10</v>
       </c>
       <c r="D136" s="8">
-        <v>45694</v>
-      </c>
-    </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46059</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A137" s="4" t="s">
         <v>30</v>
       </c>
@@ -2687,10 +2756,10 @@
         <v>4</v>
       </c>
       <c r="D137" s="8">
-        <v>45694</v>
-      </c>
-    </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46059</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
         <v>30</v>
       </c>
@@ -2701,10 +2770,10 @@
         <v>9</v>
       </c>
       <c r="D138" s="8">
-        <v>45694</v>
-      </c>
-    </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46059</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A139" s="4" t="s">
         <v>30</v>
       </c>
@@ -2715,10 +2784,10 @@
         <v>17</v>
       </c>
       <c r="D139" s="8">
-        <v>45694</v>
-      </c>
-    </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46059</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
         <v>30</v>
       </c>
@@ -2729,19 +2798,19 @@
         <v>21</v>
       </c>
       <c r="D140" s="8">
-        <v>45694</v>
-      </c>
-    </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46059</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B141" s="1"/>
     </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B142" s="1"/>
     </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B143" s="1"/>
     </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B144" s="1"/>
     </row>
     <row r="145" spans="2:2" x14ac:dyDescent="0.25">
